--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19F5695-2BB9-4144-AA0B-928EA5CB9CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5420C6-3A63-4664-A8E1-B2612A098456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1365" windowWidth="24870" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11265" yWindow="720" windowWidth="24870" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="199">
   <si>
     <t>H1U</t>
   </si>
@@ -264,9 +264,6 @@
   </si>
   <si>
     <t>Pitch Up/Down</t>
-  </si>
-  <si>
-    <t>Yaw Left/Right</t>
   </si>
   <si>
     <t>HOTAS - Quick reference -  ENHANCED - T16000 &amp; TWCS Throttle</t>
@@ -657,7 +654,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -682,6 +679,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="42">
     <border>
@@ -1260,7 +1269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1325,9 +1334,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1358,16 +1364,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1463,13 +1463,61 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1478,53 +1526,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1832,17 +1874,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="81" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="J2" s="83"/>
+      <c r="B2" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="81"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -1857,18 +1899,18 @@
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="76"/>
-      <c r="G4" s="74" t="s">
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="78"/>
+      <c r="G4" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="78"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -1883,28 +1925,28 @@
       <c r="O5"/>
     </row>
     <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="53" t="s">
+      <c r="C6" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="50" t="s">
         <v>65</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="24" t="s">
         <v>7</v>
       </c>
       <c r="K6"/>
@@ -1913,28 +1955,28 @@
       <c r="O6"/>
     </row>
     <row r="7" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="H7" s="46" t="s">
+      <c r="H7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="26" t="s">
+      <c r="J7" s="25" t="s">
         <v>66</v>
       </c>
       <c r="K7"/>
@@ -1943,25 +1985,25 @@
       <c r="O7"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="86" t="s">
         <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="86" t="s">
         <v>56</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -1976,22 +2018,22 @@
       <c r="B9" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="54" t="s">
+      <c r="C9" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="86" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="86" t="s">
         <v>58</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -2003,10 +2045,10 @@
       <c r="O9"/>
     </row>
     <row r="10" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="52" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="4">
@@ -2016,10 +2058,10 @@
       <c r="G10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="54" t="s">
+      <c r="H10" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="86" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -2031,13 +2073,13 @@
       <c r="O10"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="55" t="s">
+      <c r="H11" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="99" t="s">
         <v>71</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -2050,617 +2092,617 @@
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="56" t="s">
+      <c r="G13" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="57" t="s">
+      <c r="H13" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="57" t="s">
+      <c r="I13" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="58" t="s">
+      <c r="J13" s="55" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="84" t="s">
+      <c r="B15" s="65" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G15" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="69" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="11" t="s">
-        <v>138</v>
+      <c r="I15" s="89" t="s">
+        <v>137</v>
       </c>
       <c r="J15" s="13"/>
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="77"/>
+      <c r="B16" s="66"/>
       <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="86" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G16" s="70"/>
+      <c r="H16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="90" t="s">
+        <v>119</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="67"/>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="71"/>
+      <c r="H17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="37"/>
+      <c r="J17" s="41"/>
+      <c r="L17" s="9"/>
+    </row>
+    <row r="18" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="J18" s="45" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="69"/>
-      <c r="H16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="16" t="s">
+      <c r="G19" s="46" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="L19" s="9"/>
+    </row>
+    <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="66"/>
+      <c r="C20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="40"/>
+      <c r="J20" s="36"/>
+      <c r="L20" s="9"/>
+    </row>
+    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="67"/>
+      <c r="C21" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="73"/>
+      <c r="H21" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21" s="86" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="16" t="s">
         <v>165</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="80"/>
-      <c r="C17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I17" s="40"/>
-      <c r="J17" s="44"/>
-      <c r="L17" s="9"/>
-    </row>
-    <row r="18" spans="2:16" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G18" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="H18" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="J18" s="48" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="84" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="L19" s="9"/>
-    </row>
-    <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="77"/>
-      <c r="C20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G20" s="85" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I20" s="43"/>
-      <c r="J20" s="39"/>
-      <c r="L20" s="9"/>
-    </row>
-    <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="80"/>
-      <c r="C21" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="86"/>
-      <c r="H21" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="G22" s="87"/>
-      <c r="H22" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>194</v>
-      </c>
-      <c r="J22" s="44" t="s">
-        <v>196</v>
+      <c r="G22" s="74"/>
+      <c r="H22" s="38" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="J22" s="41" t="s">
+        <v>195</v>
       </c>
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="84" t="s">
+      <c r="B23" s="65" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="88" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="G23" s="86" t="s">
+      <c r="G23" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="H23" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>143</v>
+      <c r="H23" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>142</v>
       </c>
       <c r="J23" s="21"/>
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="77"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="86" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G24" s="86"/>
+      <c r="G24" s="73"/>
       <c r="H24" s="15" t="s">
         <v>62</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J24" s="67"/>
+        <v>134</v>
+      </c>
+      <c r="J24" s="64"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="80"/>
+      <c r="B25" s="67"/>
       <c r="C25" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="G25" s="88"/>
+      <c r="G25" s="75"/>
       <c r="H25" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="40" t="s">
-        <v>195</v>
+      <c r="I25" s="37" t="s">
+        <v>194</v>
       </c>
       <c r="J25" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L25" s="9"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9"/>
-      <c r="I26" s="31"/>
+      <c r="I26" s="30"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="65" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="G27" s="84" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="65" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I27" s="32"/>
+      <c r="I27" s="31"/>
       <c r="J27" s="13"/>
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="77"/>
+      <c r="B28" s="66"/>
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="65" t="s">
-        <v>93</v>
+      <c r="D28" s="62" t="s">
+        <v>92</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="G28" s="77"/>
+        <v>159</v>
+      </c>
+      <c r="G28" s="66"/>
       <c r="H28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="33" t="s">
-        <v>121</v>
+      <c r="I28" s="90" t="s">
+        <v>120</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="80"/>
+      <c r="B29" s="67"/>
       <c r="C29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="G29" s="80"/>
+      <c r="G29" s="67"/>
       <c r="H29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I29" s="34" t="s">
-        <v>154</v>
+      <c r="I29" s="32" t="s">
+        <v>153</v>
       </c>
       <c r="J29" s="5"/>
       <c r="L29" s="9"/>
     </row>
     <row r="30" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G30" s="8"/>
-      <c r="I30" s="31"/>
+      <c r="I30" s="30"/>
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="84" t="s">
+      <c r="B31" s="65" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="G31" s="73" t="s">
+      <c r="G31" s="69" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="P31" s="30"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="66"/>
+      <c r="C32" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="20"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I32" s="86" t="s">
+        <v>130</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L32" s="9"/>
+      <c r="P32" s="30"/>
+    </row>
+    <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="68"/>
+      <c r="C33" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="G33" s="71"/>
+      <c r="H33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="P31" s="31"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="77"/>
-      <c r="C32" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="20"/>
-      <c r="G32" s="69"/>
-      <c r="H32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="L32" s="9"/>
-      <c r="P32" s="31"/>
-    </row>
-    <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="78"/>
-      <c r="C33" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="G33" s="70"/>
-      <c r="H33" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="J33" s="7"/>
       <c r="L33" s="9"/>
-      <c r="P33" s="31"/>
+      <c r="P33" s="30"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="77" t="s">
+      <c r="B34" s="66" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" s="68" t="s">
+      <c r="G34" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I34" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="J34" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="P34" s="31"/>
+      <c r="H34" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34" s="29" t="s">
+        <v>123</v>
+      </c>
+      <c r="J34" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="77"/>
+      <c r="B35" s="66"/>
       <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="G35" s="69"/>
+      <c r="G35" s="70"/>
       <c r="H35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>132</v>
+      <c r="I35" s="86" t="s">
+        <v>131</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L35" s="9"/>
-      <c r="P35" s="31"/>
+      <c r="P35" s="30"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="78"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="70"/>
+      <c r="G36" s="71"/>
       <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="7"/>
       <c r="L36" s="9"/>
-      <c r="P36" s="31"/>
+      <c r="P36" s="30"/>
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="79" t="s">
+      <c r="B37" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E37" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="68" t="s">
+      <c r="C37" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D37" s="93" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="G37" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="H37" s="30" t="s">
+      <c r="H37" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="J37" s="39"/>
-      <c r="P37" s="31"/>
+        <v>155</v>
+      </c>
+      <c r="J37" s="36"/>
+      <c r="P37" s="30"/>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="77"/>
+      <c r="B38" s="66"/>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>95</v>
+      <c r="D38" s="86" t="s">
+        <v>94</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="G38" s="69"/>
+      <c r="G38" s="70"/>
       <c r="H38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>133</v>
+      <c r="I38" s="86" t="s">
+        <v>132</v>
       </c>
       <c r="J38" s="3"/>
       <c r="L38" s="9"/>
-      <c r="P38" s="31"/>
+      <c r="P38" s="30"/>
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="78"/>
+      <c r="B39" s="68"/>
       <c r="C39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="E39" s="38" t="s">
+      <c r="D39" s="91" t="s">
+        <v>175</v>
+      </c>
+      <c r="E39" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="G39" s="71"/>
+      <c r="H39" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I39" s="6"/>
+      <c r="J39" s="35"/>
+      <c r="L39" s="9"/>
+      <c r="P39" s="30"/>
+      <c r="Q39" s="8"/>
+    </row>
+    <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="83" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G40" s="84" t="s">
+        <v>35</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="J40" s="20"/>
+      <c r="P40" s="30"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B41" s="66"/>
+      <c r="C41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="3"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I41" s="86" t="s">
+        <v>133</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L41" s="9"/>
+      <c r="P41" s="30"/>
+    </row>
+    <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="67"/>
+      <c r="C42" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="G39" s="70"/>
-      <c r="H39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I39" s="6"/>
-      <c r="J39" s="38"/>
-      <c r="L39" s="9"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="8"/>
-    </row>
-    <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="79" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G40" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="J40" s="20"/>
-      <c r="P40" s="31"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="77"/>
-      <c r="C41" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L41" s="9"/>
-      <c r="P41" s="31"/>
-    </row>
-    <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="80"/>
-      <c r="C42" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="E42" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="G42" s="72"/>
+        <v>95</v>
+      </c>
+      <c r="G42" s="85"/>
       <c r="H42" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="5"/>
       <c r="L42" s="9"/>
-      <c r="P42" s="31"/>
+      <c r="P42" s="30"/>
     </row>
     <row r="43" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G43" s="9"/>
-      <c r="I43" s="31"/>
-      <c r="P43" s="31"/>
+      <c r="I43" s="30"/>
+      <c r="P43" s="30"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="73" t="s">
+      <c r="B44" s="69" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2668,114 +2710,114 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
-      <c r="G44" s="73" t="s">
+      <c r="G44" s="69" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I44" s="11" t="s">
-        <v>144</v>
+      <c r="I44" s="89" t="s">
+        <v>143</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L44" s="9"/>
-      <c r="P44" s="31"/>
+      <c r="P44" s="30"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="69"/>
+      <c r="B45" s="70"/>
       <c r="C45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>100</v>
+      <c r="D45" s="86" t="s">
+        <v>99</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="69"/>
+      <c r="G45" s="70"/>
       <c r="H45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>125</v>
+      <c r="I45" s="86" t="s">
+        <v>124</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="70"/>
+      <c r="B46" s="71"/>
       <c r="C46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="G46" s="70"/>
+      <c r="G46" s="71"/>
       <c r="H46" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="91" t="s">
+        <v>144</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="82" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="36"/>
+      <c r="G47" s="82" t="s">
+        <v>37</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I47" s="92" t="s">
         <v>145</v>
       </c>
-      <c r="J46" s="7" t="s">
+      <c r="J47" s="36" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="68" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="39"/>
-      <c r="G47" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="H47" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I47" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="J47" s="39" t="s">
-        <v>172</v>
-      </c>
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="69"/>
+      <c r="B48" s="70"/>
       <c r="C48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G48" s="69"/>
+      <c r="G48" s="70"/>
       <c r="H48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>126</v>
+      <c r="I48" s="86" t="s">
+        <v>125</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="70"/>
+      <c r="B49" s="71"/>
       <c r="C49" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="G49" s="70"/>
+      <c r="G49" s="71"/>
       <c r="H49" s="6" t="s">
         <v>64</v>
       </c>
@@ -2783,55 +2825,55 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="82" t="s">
         <v>16</v>
       </c>
-      <c r="C50" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="30"/>
-      <c r="E50" s="39"/>
-      <c r="G50" s="68" t="s">
+      <c r="C50" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" s="29"/>
+      <c r="E50" s="36"/>
+      <c r="G50" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="H50" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I50" s="30" t="s">
-        <v>137</v>
-      </c>
-      <c r="J50" s="39"/>
+      <c r="H50" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="69"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>101</v>
+      <c r="D51" s="86" t="s">
+        <v>100</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G51" s="69"/>
+        <v>157</v>
+      </c>
+      <c r="G51" s="70"/>
       <c r="H51" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>127</v>
+      <c r="I51" s="86" t="s">
+        <v>126</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="70"/>
+      <c r="B52" s="71"/>
       <c r="C52" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="G52" s="70"/>
+      <c r="G52" s="71"/>
       <c r="H52" s="6" t="s">
         <v>64</v>
       </c>
@@ -2839,55 +2881,55 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="68" t="s">
+      <c r="B53" s="82" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D53" s="30"/>
-      <c r="E53" s="39"/>
-      <c r="G53" s="71" t="s">
+      <c r="C53" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="29"/>
+      <c r="E53" s="36"/>
+      <c r="G53" s="84" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="69"/>
+      <c r="B54" s="70"/>
       <c r="C54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>157</v>
+      <c r="D54" s="86" t="s">
+        <v>156</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G54" s="69"/>
+        <v>163</v>
+      </c>
+      <c r="G54" s="70"/>
       <c r="H54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I54" s="2" t="s">
-        <v>128</v>
+      <c r="I54" s="86" t="s">
+        <v>127</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="70"/>
+      <c r="B55" s="71"/>
       <c r="C55" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
-      <c r="G55" s="72"/>
+      <c r="G55" s="85"/>
       <c r="H55" s="4" t="s">
         <v>64</v>
       </c>
@@ -2895,59 +2937,59 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="68" t="s">
+      <c r="B56" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="39"/>
+      <c r="C56" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" s="29"/>
+      <c r="E56" s="36"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="69"/>
+      <c r="B57" s="70"/>
       <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G57" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="69" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="70"/>
+      <c r="B58" s="71"/>
       <c r="C58" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="G58" s="69"/>
+      <c r="G58" s="70"/>
       <c r="H58" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="71" t="s">
+      <c r="B59" s="84" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
@@ -2955,55 +2997,55 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
-      <c r="G59" s="70"/>
+      <c r="G59" s="71"/>
       <c r="H59" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="69"/>
+      <c r="B60" s="70"/>
       <c r="C60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="65" t="s">
-        <v>102</v>
+      <c r="D60" s="94" t="s">
+        <v>101</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="G60" s="68" t="s">
+      <c r="G60" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I60" s="30"/>
-      <c r="J60" s="39"/>
+      <c r="H60" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I60" s="29"/>
+      <c r="J60" s="36"/>
     </row>
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="72"/>
+      <c r="B61" s="85"/>
       <c r="C61" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
-      <c r="G61" s="69"/>
+      <c r="G61" s="70"/>
       <c r="H61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="70"/>
+      <c r="G62" s="71"/>
       <c r="H62" s="6" t="s">
         <v>64</v>
       </c>
@@ -3011,51 +3053,51 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="73" t="s">
+      <c r="B63" s="69" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="66"/>
+      <c r="D63" s="63"/>
       <c r="E63" s="13"/>
-      <c r="G63" s="68" t="s">
+      <c r="G63" s="82" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="I63" s="30"/>
-      <c r="J63" s="39"/>
+      <c r="H63" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="I63" s="29"/>
+      <c r="J63" s="36"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="69"/>
+      <c r="B64" s="70"/>
       <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>183</v>
+      <c r="D64" s="86" t="s">
+        <v>182</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="G64" s="69"/>
+      <c r="G64" s="70"/>
       <c r="H64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I64" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="70"/>
+      <c r="B65" s="71"/>
       <c r="C65" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
-      <c r="G65" s="70"/>
+      <c r="G65" s="71"/>
       <c r="H65" s="6" t="s">
         <v>64</v>
       </c>
@@ -3063,15 +3105,15 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="68" t="s">
+      <c r="B66" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D66" s="30"/>
-      <c r="E66" s="39"/>
-      <c r="G66" s="71" t="s">
+      <c r="C66" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" s="29"/>
+      <c r="E66" s="36"/>
+      <c r="G66" s="84" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
@@ -3081,31 +3123,31 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="69"/>
+      <c r="B67" s="70"/>
       <c r="C67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-      <c r="G67" s="69"/>
+      <c r="G67" s="70"/>
       <c r="H67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="70"/>
+      <c r="B68" s="71"/>
       <c r="C68" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="G68" s="72"/>
+      <c r="G68" s="85"/>
       <c r="H68" s="4" t="s">
         <v>64</v>
       </c>
@@ -3113,35 +3155,35 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="68" t="s">
+      <c r="B69" s="82" t="s">
         <v>22</v>
       </c>
-      <c r="C69" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D69" s="30"/>
-      <c r="E69" s="39"/>
+      <c r="C69" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D69" s="29"/>
+      <c r="E69" s="36"/>
     </row>
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="69"/>
+      <c r="B70" s="70"/>
       <c r="C70" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D70" s="86" t="s">
+        <v>183</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G70" s="74" t="s">
-        <v>78</v>
-      </c>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="76"/>
+      <c r="G70" s="76" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" s="77"/>
+      <c r="I70" s="77"/>
+      <c r="J70" s="78"/>
     </row>
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="70"/>
+      <c r="B71" s="71"/>
       <c r="C71" s="6" t="s">
         <v>64</v>
       </c>
@@ -3149,64 +3191,64 @@
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="68" t="s">
+      <c r="B72" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="29" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E72" s="36"/>
+      <c r="G72" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H72" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="I72" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B73" s="70"/>
+      <c r="C73" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="3"/>
+      <c r="G73" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="H73" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="I73" s="86" t="s">
+        <v>56</v>
+      </c>
+      <c r="J73" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="71"/>
+      <c r="C74" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D74" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E72" s="39"/>
-      <c r="G72" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="H72" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="J72" s="25" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="69"/>
-      <c r="C73" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E73" s="3"/>
-      <c r="G73" s="29" t="s">
+      <c r="E74" s="7"/>
+      <c r="G74" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="H73" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J73" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="70"/>
-      <c r="C74" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E74" s="7"/>
-      <c r="G74" s="27" t="s">
-        <v>81</v>
-      </c>
-      <c r="H74" s="54" t="s">
+      <c r="H74" s="51" t="s">
         <v>65</v>
       </c>
       <c r="I74" s="2">
@@ -3215,18 +3257,18 @@
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="68" t="s">
+      <c r="B75" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="C75" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D75" s="30"/>
-      <c r="E75" s="39"/>
-      <c r="G75" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="H75" s="55" t="s">
+      <c r="C75" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="D75" s="29"/>
+      <c r="E75" s="36"/>
+      <c r="G75" s="56" t="s">
+        <v>81</v>
+      </c>
+      <c r="H75" s="52" t="s">
         <v>65</v>
       </c>
       <c r="I75" s="4">
@@ -3235,58 +3277,58 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="69"/>
+      <c r="B76" s="70"/>
       <c r="C76" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
-      <c r="J76" s="61"/>
+        <v>192</v>
+      </c>
+      <c r="G76" s="58"/>
+      <c r="H76" s="58"/>
+      <c r="I76" s="58"/>
+      <c r="J76" s="58"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="70"/>
+      <c r="B77" s="71"/>
       <c r="C77" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="7"/>
-      <c r="G77" s="60" t="s">
-        <v>83</v>
-      </c>
-      <c r="H77" s="62" t="s">
+      <c r="G77" s="57" t="s">
+        <v>82</v>
+      </c>
+      <c r="H77" s="59" t="s">
         <v>65</v>
       </c>
       <c r="I77" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="J77" s="26" t="s">
-        <v>79</v>
+      <c r="J77" s="25" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="71" t="s">
+      <c r="B78" s="84" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="19" t="s">
-        <v>140</v>
+      <c r="D78" s="95" t="s">
+        <v>139</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="G78" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="H78" s="63" t="s">
+        <v>188</v>
+      </c>
+      <c r="G78" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H78" s="60" t="s">
         <v>65</v>
       </c>
       <c r="I78" s="2">
@@ -3295,20 +3337,20 @@
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="69"/>
+      <c r="B79" s="70"/>
       <c r="C79" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>141</v>
+      <c r="D79" s="96" t="s">
+        <v>140</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G79" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="H79" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="G79" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="H79" s="61" t="s">
         <v>65</v>
       </c>
       <c r="I79" s="4">
@@ -3317,44 +3359,19 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="72"/>
+      <c r="B80" s="85"/>
       <c r="C80" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D80" s="4" t="s">
-        <v>139</v>
+      <c r="D80" s="97" t="s">
+        <v>138</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G44:G46"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B78:B80"/>
@@ -3370,9 +3387,34 @@
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G31:G33"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="40" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5420C6-3A63-4664-A8E1-B2612A098456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1691218C-F631-4034-90B8-1A66D79003A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11265" yWindow="720" windowWidth="24870" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5595" yWindow="450" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1269,7 +1269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1454,13 +1454,52 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1525,48 +1564,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1874,17 +1871,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="81"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="94"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -1899,18 +1896,18 @@
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="76" t="s">
+      <c r="B4" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78"/>
-      <c r="G4" s="76" t="s">
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="91"/>
+      <c r="G4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="78"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="91"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -1961,7 +1958,7 @@
       <c r="C7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="98" t="s">
+      <c r="D7" s="76" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="25" t="s">
@@ -1973,7 +1970,7 @@
       <c r="H7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="98" t="s">
+      <c r="I7" s="76" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="25" t="s">
@@ -1991,7 +1988,7 @@
       <c r="C8" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="64" t="s">
         <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -2003,7 +2000,7 @@
       <c r="H8" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="86" t="s">
+      <c r="I8" s="64" t="s">
         <v>56</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -2021,7 +2018,7 @@
       <c r="C9" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="86" t="s">
+      <c r="D9" s="64" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -2033,7 +2030,7 @@
       <c r="H9" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="64" t="s">
         <v>58</v>
       </c>
       <c r="J9" s="3" t="s">
@@ -2061,7 +2058,7 @@
       <c r="H10" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="I10" s="86" t="s">
+      <c r="I10" s="64" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="3" t="s">
@@ -2079,7 +2076,7 @@
       <c r="H11" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="99" t="s">
+      <c r="I11" s="77" t="s">
         <v>71</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -2119,7 +2116,7 @@
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="78" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -2131,34 +2128,34 @@
       <c r="E15" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="82" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="89" t="s">
+      <c r="I15" s="67" t="s">
         <v>137</v>
       </c>
       <c r="J15" s="13"/>
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="66"/>
+      <c r="B16" s="79"/>
       <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="64" t="s">
         <v>106</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="70"/>
+      <c r="G16" s="83"/>
       <c r="H16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="90" t="s">
+      <c r="I16" s="68" t="s">
         <v>119</v>
       </c>
       <c r="J16" s="16" t="s">
@@ -2167,17 +2164,17 @@
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="67"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D17" s="87" t="s">
+      <c r="D17" s="65" t="s">
         <v>87</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="71"/>
+      <c r="G17" s="84"/>
       <c r="H17" s="6" t="s">
         <v>64</v>
       </c>
@@ -2200,7 +2197,7 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="65" t="s">
+      <c r="B19" s="78" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -2227,17 +2224,17 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="66"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="64" t="s">
         <v>108</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="72" t="s">
+      <c r="G20" s="85" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="29" t="s">
@@ -2248,7 +2245,7 @@
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="67"/>
+      <c r="B21" s="80"/>
       <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
@@ -2258,11 +2255,11 @@
       <c r="E21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="73"/>
+      <c r="G21" s="86"/>
       <c r="H21" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="I21" s="86" t="s">
+      <c r="I21" s="64" t="s">
         <v>141</v>
       </c>
       <c r="J21" s="16" t="s">
@@ -2271,7 +2268,7 @@
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="G22" s="74"/>
+      <c r="G22" s="87"/>
       <c r="H22" s="38" t="s">
         <v>64</v>
       </c>
@@ -2284,19 +2281,19 @@
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="65" t="s">
+      <c r="B23" s="78" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="88" t="s">
+      <c r="D23" s="66" t="s">
         <v>111</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="G23" s="73" t="s">
+      <c r="G23" s="86" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="39" t="s">
@@ -2309,37 +2306,37 @@
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="66"/>
+      <c r="B24" s="79"/>
       <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="86" t="s">
+      <c r="D24" s="64" t="s">
         <v>109</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="73"/>
+      <c r="G24" s="86"/>
       <c r="H24" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="I24" s="64" t="s">
         <v>134</v>
       </c>
-      <c r="J24" s="64"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="67"/>
+      <c r="B25" s="80"/>
       <c r="C25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="77" t="s">
         <v>151</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="G25" s="75"/>
+      <c r="G25" s="88"/>
       <c r="H25" s="17" t="s">
         <v>64</v>
       </c>
@@ -2356,19 +2353,19 @@
       <c r="I26" s="30"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="78" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="67" t="s">
         <v>91</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="65" t="s">
+      <c r="G27" s="78" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -2379,21 +2376,21 @@
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="66"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="62" t="s">
+      <c r="D28" s="72" t="s">
         <v>92</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="G28" s="66"/>
+      <c r="G28" s="79"/>
       <c r="H28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="90" t="s">
+      <c r="I28" s="68" t="s">
         <v>120</v>
       </c>
       <c r="J28" s="3" t="s">
@@ -2401,17 +2398,17 @@
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="67"/>
+      <c r="B29" s="80"/>
       <c r="C29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="77" t="s">
         <v>113</v>
       </c>
       <c r="E29" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G29" s="67"/>
+      <c r="G29" s="80"/>
       <c r="H29" s="4" t="s">
         <v>64</v>
       </c>
@@ -2427,7 +2424,7 @@
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="65" t="s">
+      <c r="B31" s="78" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -2437,13 +2434,13 @@
         <v>105</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="G31" s="69" t="s">
+      <c r="G31" s="82" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="67" t="s">
         <v>121</v>
       </c>
       <c r="J31" s="13" t="s">
@@ -2452,19 +2449,19 @@
       <c r="P31" s="30"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="66"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D32" s="86" t="s">
+      <c r="D32" s="64" t="s">
         <v>93</v>
       </c>
       <c r="E32" s="20"/>
-      <c r="G32" s="70"/>
+      <c r="G32" s="83"/>
       <c r="H32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I32" s="86" t="s">
+      <c r="I32" s="64" t="s">
         <v>130</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -2474,7 +2471,7 @@
       <c r="P32" s="30"/>
     </row>
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="68"/>
+      <c r="B33" s="81"/>
       <c r="C33" s="34" t="s">
         <v>64</v>
       </c>
@@ -2482,7 +2479,7 @@
         <v>98</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="G33" s="71"/>
+      <c r="G33" s="84"/>
       <c r="H33" s="6" t="s">
         <v>64</v>
       </c>
@@ -2494,7 +2491,7 @@
       <c r="P33" s="30"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="66" t="s">
+      <c r="B34" s="79" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
@@ -2504,7 +2501,7 @@
         <v>97</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" s="82" t="s">
+      <c r="G34" s="95" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="29" t="s">
@@ -2519,7 +2516,7 @@
       <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="66"/>
+      <c r="B35" s="79"/>
       <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
@@ -2529,11 +2526,11 @@
       <c r="E35" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G35" s="70"/>
+      <c r="G35" s="83"/>
       <c r="H35" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="86" t="s">
+      <c r="I35" s="64" t="s">
         <v>131</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -2543,7 +2540,7 @@
       <c r="P35" s="30"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="68"/>
+      <c r="B36" s="81"/>
       <c r="C36" s="6" t="s">
         <v>64</v>
       </c>
@@ -2551,7 +2548,7 @@
         <v>96</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="71"/>
+      <c r="G36" s="84"/>
       <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
@@ -2562,19 +2559,19 @@
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="83" t="s">
+      <c r="B37" s="96" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="93" t="s">
+      <c r="D37" s="71" t="s">
         <v>115</v>
       </c>
       <c r="E37" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="G37" s="82" t="s">
+      <c r="G37" s="95" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="29" t="s">
@@ -2588,19 +2585,19 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="66"/>
+      <c r="B38" s="79"/>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D38" s="86" t="s">
+      <c r="D38" s="64" t="s">
         <v>94</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="G38" s="70"/>
+      <c r="G38" s="83"/>
       <c r="H38" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I38" s="86" t="s">
+      <c r="I38" s="64" t="s">
         <v>132</v>
       </c>
       <c r="J38" s="3"/>
@@ -2609,17 +2606,17 @@
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="68"/>
+      <c r="B39" s="81"/>
       <c r="C39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="91" t="s">
+      <c r="D39" s="69" t="s">
         <v>175</v>
       </c>
       <c r="E39" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="G39" s="71"/>
+      <c r="G39" s="84"/>
       <c r="H39" s="6" t="s">
         <v>64</v>
       </c>
@@ -2630,19 +2627,19 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="83" t="s">
+      <c r="B40" s="96" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D40" s="71" t="s">
         <v>161</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G40" s="84" t="s">
+      <c r="G40" s="97" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
@@ -2655,19 +2652,19 @@
       <c r="P40" s="30"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="66"/>
+      <c r="B41" s="79"/>
       <c r="C41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="64" t="s">
         <v>116</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="G41" s="70"/>
+      <c r="G41" s="83"/>
       <c r="H41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I41" s="86" t="s">
+      <c r="I41" s="64" t="s">
         <v>133</v>
       </c>
       <c r="J41" s="3" t="s">
@@ -2677,17 +2674,17 @@
       <c r="P41" s="30"/>
     </row>
     <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="67"/>
+      <c r="B42" s="80"/>
       <c r="C42" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="77" t="s">
         <v>160</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G42" s="85"/>
+      <c r="G42" s="98"/>
       <c r="H42" s="4" t="s">
         <v>64</v>
       </c>
@@ -2702,7 +2699,7 @@
       <c r="P43" s="30"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="82" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2710,13 +2707,13 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
-      <c r="G44" s="69" t="s">
+      <c r="G44" s="82" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I44" s="89" t="s">
+      <c r="I44" s="67" t="s">
         <v>143</v>
       </c>
       <c r="J44" s="13" t="s">
@@ -2726,19 +2723,19 @@
       <c r="P44" s="30"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="70"/>
+      <c r="B45" s="83"/>
       <c r="C45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D45" s="86" t="s">
+      <c r="D45" s="64" t="s">
         <v>99</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="70"/>
+      <c r="G45" s="83"/>
       <c r="H45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I45" s="86" t="s">
+      <c r="I45" s="64" t="s">
         <v>124</v>
       </c>
       <c r="J45" s="3" t="s">
@@ -2747,17 +2744,17 @@
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="71"/>
+      <c r="B46" s="84"/>
       <c r="C46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="G46" s="71"/>
+      <c r="G46" s="84"/>
       <c r="H46" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I46" s="91" t="s">
+      <c r="I46" s="69" t="s">
         <v>144</v>
       </c>
       <c r="J46" s="7" t="s">
@@ -2765,7 +2762,7 @@
       </c>
     </row>
     <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="82" t="s">
+      <c r="B47" s="95" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="29" t="s">
@@ -2773,13 +2770,13 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="36"/>
-      <c r="G47" s="82" t="s">
+      <c r="G47" s="95" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="I47" s="92" t="s">
+      <c r="I47" s="70" t="s">
         <v>145</v>
       </c>
       <c r="J47" s="36" t="s">
@@ -2788,21 +2785,21 @@
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="70"/>
+      <c r="B48" s="83"/>
       <c r="C48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="64" t="s">
         <v>197</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="G48" s="70"/>
+      <c r="G48" s="83"/>
       <c r="H48" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I48" s="86" t="s">
+      <c r="I48" s="64" t="s">
         <v>125</v>
       </c>
       <c r="J48" s="3" t="s">
@@ -2811,13 +2808,13 @@
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="71"/>
+      <c r="B49" s="84"/>
       <c r="C49" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="G49" s="71"/>
+      <c r="G49" s="84"/>
       <c r="H49" s="6" t="s">
         <v>64</v>
       </c>
@@ -2825,7 +2822,7 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="82" t="s">
+      <c r="B50" s="95" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="29" t="s">
@@ -2833,7 +2830,7 @@
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="36"/>
-      <c r="G50" s="82" t="s">
+      <c r="G50" s="95" t="s">
         <v>38</v>
       </c>
       <c r="H50" s="29" t="s">
@@ -2845,21 +2842,21 @@
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="70"/>
+      <c r="B51" s="83"/>
       <c r="C51" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D51" s="86" t="s">
+      <c r="D51" s="64" t="s">
         <v>100</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G51" s="70"/>
+      <c r="G51" s="83"/>
       <c r="H51" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I51" s="86" t="s">
+      <c r="I51" s="64" t="s">
         <v>126</v>
       </c>
       <c r="J51" s="3" t="s">
@@ -2867,13 +2864,13 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="71"/>
+      <c r="B52" s="84"/>
       <c r="C52" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="G52" s="71"/>
+      <c r="G52" s="84"/>
       <c r="H52" s="6" t="s">
         <v>64</v>
       </c>
@@ -2881,7 +2878,7 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="82" t="s">
+      <c r="B53" s="95" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="29" t="s">
@@ -2889,7 +2886,7 @@
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="36"/>
-      <c r="G53" s="84" t="s">
+      <c r="G53" s="97" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
@@ -2901,21 +2898,21 @@
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="70"/>
+      <c r="B54" s="83"/>
       <c r="C54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="86" t="s">
+      <c r="D54" s="64" t="s">
         <v>156</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G54" s="70"/>
+      <c r="G54" s="83"/>
       <c r="H54" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I54" s="86" t="s">
+      <c r="I54" s="64" t="s">
         <v>127</v>
       </c>
       <c r="J54" s="3" t="s">
@@ -2923,13 +2920,13 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="71"/>
+      <c r="B55" s="84"/>
       <c r="C55" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
-      <c r="G55" s="85"/>
+      <c r="G55" s="98"/>
       <c r="H55" s="4" t="s">
         <v>64</v>
       </c>
@@ -2937,7 +2934,7 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="82" t="s">
+      <c r="B56" s="95" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="29" t="s">
@@ -2947,7 +2944,7 @@
       <c r="E56" s="36"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="70"/>
+      <c r="B57" s="83"/>
       <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
@@ -2957,7 +2954,7 @@
       <c r="E57" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G57" s="69" t="s">
+      <c r="G57" s="82" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
@@ -2971,13 +2968,13 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="71"/>
+      <c r="B58" s="84"/>
       <c r="C58" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="G58" s="70"/>
+      <c r="G58" s="83"/>
       <c r="H58" s="2" t="s">
         <v>62</v>
       </c>
@@ -2989,7 +2986,7 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="84" t="s">
+      <c r="B59" s="97" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
@@ -2997,7 +2994,7 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
-      <c r="G59" s="71"/>
+      <c r="G59" s="84"/>
       <c r="H59" s="6" t="s">
         <v>64</v>
       </c>
@@ -3009,15 +3006,15 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="70"/>
+      <c r="B60" s="83"/>
       <c r="C60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="94" t="s">
+      <c r="D60" s="72" t="s">
         <v>101</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="G60" s="82" t="s">
+      <c r="G60" s="95" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="29" t="s">
@@ -3027,17 +3024,17 @@
       <c r="J60" s="36"/>
     </row>
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="85"/>
+      <c r="B61" s="98"/>
       <c r="C61" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
-      <c r="G61" s="70"/>
+      <c r="G61" s="83"/>
       <c r="H61" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I61" s="2" t="s">
+      <c r="I61" s="64" t="s">
         <v>146</v>
       </c>
       <c r="J61" s="3" t="s">
@@ -3045,7 +3042,7 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="71"/>
+      <c r="G62" s="84"/>
       <c r="H62" s="6" t="s">
         <v>64</v>
       </c>
@@ -3053,15 +3050,15 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="69" t="s">
+      <c r="B63" s="82" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D63" s="63"/>
+      <c r="D63" s="62"/>
       <c r="E63" s="13"/>
-      <c r="G63" s="82" t="s">
+      <c r="G63" s="95" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="29" t="s">
@@ -3071,19 +3068,19 @@
       <c r="J63" s="36"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="70"/>
+      <c r="B64" s="83"/>
       <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D64" s="86" t="s">
+      <c r="D64" s="64" t="s">
         <v>182</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="G64" s="70"/>
+      <c r="G64" s="83"/>
       <c r="H64" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I64" s="2" t="s">
+      <c r="I64" s="64" t="s">
         <v>147</v>
       </c>
       <c r="J64" s="3" t="s">
@@ -3091,13 +3088,13 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="71"/>
+      <c r="B65" s="84"/>
       <c r="C65" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
-      <c r="G65" s="71"/>
+      <c r="G65" s="84"/>
       <c r="H65" s="6" t="s">
         <v>64</v>
       </c>
@@ -3105,7 +3102,7 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="82" t="s">
+      <c r="B66" s="95" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="29" t="s">
@@ -3113,7 +3110,7 @@
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="36"/>
-      <c r="G66" s="84" t="s">
+      <c r="G66" s="97" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
@@ -3123,13 +3120,13 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="70"/>
+      <c r="B67" s="83"/>
       <c r="C67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-      <c r="G67" s="70"/>
+      <c r="G67" s="83"/>
       <c r="H67" s="2" t="s">
         <v>62</v>
       </c>
@@ -3141,13 +3138,13 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="71"/>
+      <c r="B68" s="84"/>
       <c r="C68" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="G68" s="85"/>
+      <c r="G68" s="98"/>
       <c r="H68" s="4" t="s">
         <v>64</v>
       </c>
@@ -3155,7 +3152,7 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="82" t="s">
+      <c r="B69" s="95" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="29" t="s">
@@ -3165,25 +3162,25 @@
       <c r="E69" s="36"/>
     </row>
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="70"/>
+      <c r="B70" s="83"/>
       <c r="C70" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D70" s="86" t="s">
+      <c r="D70" s="64" t="s">
         <v>183</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G70" s="76" t="s">
+      <c r="G70" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="H70" s="77"/>
-      <c r="I70" s="77"/>
-      <c r="J70" s="78"/>
+      <c r="H70" s="90"/>
+      <c r="I70" s="90"/>
+      <c r="J70" s="91"/>
     </row>
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="71"/>
+      <c r="B71" s="84"/>
       <c r="C71" s="6" t="s">
         <v>64</v>
       </c>
@@ -3191,7 +3188,7 @@
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="82" t="s">
+      <c r="B72" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="29" t="s">
@@ -3215,7 +3212,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="70"/>
+      <c r="B73" s="83"/>
       <c r="C73" s="2" t="s">
         <v>62</v>
       </c>
@@ -3229,7 +3226,7 @@
       <c r="H73" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I73" s="86" t="s">
+      <c r="I73" s="64" t="s">
         <v>56</v>
       </c>
       <c r="J73" s="25" t="s">
@@ -3237,7 +3234,7 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="71"/>
+      <c r="B74" s="84"/>
       <c r="C74" s="6" t="s">
         <v>64</v>
       </c>
@@ -3257,7 +3254,7 @@
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="82" t="s">
+      <c r="B75" s="95" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="29" t="s">
@@ -3277,7 +3274,7 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="70"/>
+      <c r="B76" s="83"/>
       <c r="C76" s="2" t="s">
         <v>62</v>
       </c>
@@ -3293,7 +3290,7 @@
       <c r="J76" s="58"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="71"/>
+      <c r="B77" s="84"/>
       <c r="C77" s="6" t="s">
         <v>64</v>
       </c>
@@ -3313,13 +3310,13 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="84" t="s">
+      <c r="B78" s="97" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="95" t="s">
+      <c r="D78" s="73" t="s">
         <v>139</v>
       </c>
       <c r="E78" s="20" t="s">
@@ -3337,11 +3334,11 @@
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="70"/>
+      <c r="B79" s="83"/>
       <c r="C79" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D79" s="96" t="s">
+      <c r="D79" s="74" t="s">
         <v>140</v>
       </c>
       <c r="E79" s="3" t="s">
@@ -3359,11 +3356,11 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="85"/>
+      <c r="B80" s="98"/>
       <c r="C80" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D80" s="97" t="s">
+      <c r="D80" s="75" t="s">
         <v>138</v>
       </c>
       <c r="E80" s="5" t="s">

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1691218C-F631-4034-90B8-1A66D79003A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F720A7-BD21-4168-B42F-60C499659235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="450" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18150" yWindow="360" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="197">
   <si>
     <t>H1U</t>
   </si>
@@ -369,12 +369,6 @@
   </si>
   <si>
     <t>FAOff ON/OFF</t>
-  </si>
-  <si>
-    <t>tgEnhancedFAOFF(1)</t>
-  </si>
-  <si>
-    <t>JSMouse Emulation</t>
   </si>
   <si>
     <t>tgXAxis(SET)</t>
@@ -1269,7 +1263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1464,9 +1458,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1871,17 +1862,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="94"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="93"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -1896,18 +1887,18 @@
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="91"/>
-      <c r="G4" s="89" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="G4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="91"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="90"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -1958,7 +1949,7 @@
       <c r="C7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="75" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="25" t="s">
@@ -1970,7 +1961,7 @@
       <c r="H7" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="I7" s="76" t="s">
+      <c r="I7" s="75" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="25" t="s">
@@ -2076,7 +2067,7 @@
       <c r="H11" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="77" t="s">
+      <c r="I11" s="76" t="s">
         <v>71</v>
       </c>
       <c r="J11" s="5" t="s">
@@ -2116,7 +2107,7 @@
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="77" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -2128,20 +2119,20 @@
       <c r="E15" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="81" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I15" s="67" t="s">
-        <v>137</v>
+      <c r="I15" s="66" t="s">
+        <v>135</v>
       </c>
       <c r="J15" s="13"/>
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="79"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
@@ -2151,20 +2142,20 @@
       <c r="E16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="83"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="68" t="s">
-        <v>119</v>
+      <c r="I16" s="67" t="s">
+        <v>117</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="80"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="4" t="s">
         <v>64</v>
       </c>
@@ -2174,7 +2165,7 @@
       <c r="E17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G17" s="84"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="6" t="s">
         <v>64</v>
       </c>
@@ -2197,7 +2188,7 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="78" t="s">
+      <c r="B19" s="77" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -2224,7 +2215,7 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="79"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="2" t="s">
         <v>62</v>
       </c>
@@ -2234,18 +2225,22 @@
       <c r="E20" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="85" t="s">
+      <c r="G20" s="84" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="36"/>
+      <c r="I20" s="40" t="s">
+        <v>191</v>
+      </c>
+      <c r="J20" s="36" t="s">
+        <v>193</v>
+      </c>
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="80"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
@@ -2255,97 +2250,89 @@
       <c r="E21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="86"/>
+      <c r="G21" s="85"/>
       <c r="H21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="I21" s="64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="G22" s="87"/>
+      <c r="G22" s="86"/>
       <c r="H22" s="38" t="s">
         <v>64</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J22" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
+      <c r="B23" s="77" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="66" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="G23" s="86" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="85" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="39" t="s">
         <v>63</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J23" s="21"/>
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="79"/>
+      <c r="B24" s="78"/>
       <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="64" t="s">
+      <c r="D24" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="86"/>
+      <c r="G24" s="85"/>
       <c r="H24" s="15" t="s">
         <v>62</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J24" s="63"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="80"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="77" t="s">
-        <v>151</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G25" s="88"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>196</v>
-      </c>
+      <c r="I25" s="37"/>
+      <c r="J25" s="18"/>
       <c r="L25" s="9"/>
     </row>
     <row r="26" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2353,19 +2340,19 @@
       <c r="I26" s="30"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="78" t="s">
+      <c r="B27" s="77" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="67" t="s">
+      <c r="D27" s="66" t="s">
         <v>91</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="G27" s="78" t="s">
+        <v>156</v>
+      </c>
+      <c r="G27" s="77" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -2376,44 +2363,44 @@
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="79"/>
+      <c r="B28" s="78"/>
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="72" t="s">
+      <c r="D28" s="71" t="s">
         <v>92</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="G28" s="79"/>
+        <v>157</v>
+      </c>
+      <c r="G28" s="78"/>
       <c r="H28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="68" t="s">
-        <v>120</v>
+      <c r="I28" s="67" t="s">
+        <v>118</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="80"/>
+      <c r="B29" s="79"/>
       <c r="C29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="77" t="s">
-        <v>113</v>
+      <c r="D29" s="76" t="s">
+        <v>111</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>114</v>
-      </c>
-      <c r="G29" s="80"/>
+        <v>112</v>
+      </c>
+      <c r="G29" s="79"/>
       <c r="H29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J29" s="5"/>
       <c r="L29" s="9"/>
@@ -2424,7 +2411,7 @@
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="78" t="s">
+      <c r="B31" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -2434,22 +2421,22 @@
         <v>105</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="81" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="67" t="s">
-        <v>121</v>
+      <c r="I31" s="66" t="s">
+        <v>119</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="P31" s="30"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="79"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="19" t="s">
         <v>62</v>
       </c>
@@ -2457,21 +2444,21 @@
         <v>93</v>
       </c>
       <c r="E32" s="20"/>
-      <c r="G32" s="83"/>
+      <c r="G32" s="82"/>
       <c r="H32" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I32" s="64" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="L32" s="9"/>
       <c r="P32" s="30"/>
     </row>
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="81"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="34" t="s">
         <v>64</v>
       </c>
@@ -2479,19 +2466,19 @@
         <v>98</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="G33" s="84"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J33" s="7"/>
       <c r="L33" s="9"/>
       <c r="P33" s="30"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="79" t="s">
+      <c r="B34" s="78" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
@@ -2501,46 +2488,46 @@
         <v>97</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" s="95" t="s">
+      <c r="G34" s="94" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="79"/>
+      <c r="B35" s="78"/>
       <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="G35" s="83"/>
+        <v>116</v>
+      </c>
+      <c r="G35" s="82"/>
       <c r="H35" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I35" s="64" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L35" s="9"/>
       <c r="P35" s="30"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="81"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="6" t="s">
         <v>64</v>
       </c>
@@ -2548,7 +2535,7 @@
         <v>96</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="84"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
@@ -2559,33 +2546,33 @@
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="95" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D37" s="71" t="s">
-        <v>115</v>
+      <c r="D37" s="70" t="s">
+        <v>113</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="G37" s="95" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="94" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J37" s="36"/>
       <c r="P37" s="30"/>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="79"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
@@ -2593,12 +2580,12 @@
         <v>94</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="G38" s="83"/>
+      <c r="G38" s="82"/>
       <c r="H38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I38" s="64" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J38" s="3"/>
       <c r="L38" s="9"/>
@@ -2606,17 +2593,17 @@
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="81"/>
+      <c r="B39" s="80"/>
       <c r="C39" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="69" t="s">
-        <v>175</v>
+      <c r="D39" s="68" t="s">
+        <v>173</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" s="84"/>
+        <v>157</v>
+      </c>
+      <c r="G39" s="83"/>
       <c r="H39" s="6" t="s">
         <v>64</v>
       </c>
@@ -2627,64 +2614,64 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="96" t="s">
+      <c r="B40" s="95" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="71" t="s">
-        <v>161</v>
+      <c r="D40" s="70" t="s">
+        <v>159</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="G40" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="G40" s="96" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J40" s="20"/>
       <c r="P40" s="30"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="79"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D41" s="64" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="G41" s="83"/>
+      <c r="G41" s="82"/>
       <c r="H41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I41" s="64" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L41" s="9"/>
       <c r="P41" s="30"/>
     </row>
     <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="80"/>
+      <c r="B42" s="79"/>
       <c r="C42" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D42" s="77" t="s">
-        <v>160</v>
+      <c r="D42" s="76" t="s">
+        <v>158</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="G42" s="98"/>
+      <c r="G42" s="97"/>
       <c r="H42" s="4" t="s">
         <v>64</v>
       </c>
@@ -2699,7 +2686,7 @@
       <c r="P43" s="30"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="81" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2707,23 +2694,23 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
-      <c r="G44" s="82" t="s">
+      <c r="G44" s="81" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I44" s="67" t="s">
-        <v>143</v>
+      <c r="I44" s="66" t="s">
+        <v>141</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="L44" s="9"/>
       <c r="P44" s="30"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="83"/>
+      <c r="B45" s="82"/>
       <c r="C45" s="2" t="s">
         <v>62</v>
       </c>
@@ -2731,38 +2718,38 @@
         <v>99</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="83"/>
+      <c r="G45" s="82"/>
       <c r="H45" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I45" s="64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="84"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="G46" s="84"/>
+      <c r="G46" s="83"/>
       <c r="H46" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I46" s="69" t="s">
-        <v>144</v>
+      <c r="I46" s="68" t="s">
+        <v>142</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="95" t="s">
+      <c r="B47" s="94" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="29" t="s">
@@ -2770,51 +2757,51 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="36"/>
-      <c r="G47" s="95" t="s">
+      <c r="G47" s="94" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="I47" s="70" t="s">
-        <v>145</v>
+      <c r="I47" s="69" t="s">
+        <v>143</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="83"/>
+      <c r="B48" s="82"/>
       <c r="C48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D48" s="64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G48" s="83"/>
+        <v>196</v>
+      </c>
+      <c r="G48" s="82"/>
       <c r="H48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I48" s="64" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="84"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="G49" s="84"/>
+      <c r="G49" s="83"/>
       <c r="H49" s="6" t="s">
         <v>64</v>
       </c>
@@ -2822,7 +2809,7 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="95" t="s">
+      <c r="B50" s="94" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="29" t="s">
@@ -2830,19 +2817,19 @@
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="36"/>
-      <c r="G50" s="95" t="s">
+      <c r="G50" s="94" t="s">
         <v>38</v>
       </c>
       <c r="H50" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="83"/>
+      <c r="B51" s="82"/>
       <c r="C51" s="2" t="s">
         <v>62</v>
       </c>
@@ -2850,27 +2837,27 @@
         <v>100</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G51" s="83"/>
+        <v>155</v>
+      </c>
+      <c r="G51" s="82"/>
       <c r="H51" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I51" s="64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="84"/>
+      <c r="B52" s="83"/>
       <c r="C52" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="G52" s="84"/>
+      <c r="G52" s="83"/>
       <c r="H52" s="6" t="s">
         <v>64</v>
       </c>
@@ -2878,7 +2865,7 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="95" t="s">
+      <c r="B53" s="94" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="29" t="s">
@@ -2886,47 +2873,47 @@
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="36"/>
-      <c r="G53" s="97" t="s">
+      <c r="G53" s="96" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="83"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D54" s="64" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G54" s="83"/>
+        <v>161</v>
+      </c>
+      <c r="G54" s="82"/>
       <c r="H54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I54" s="64" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="84"/>
+      <c r="B55" s="83"/>
       <c r="C55" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
-      <c r="G55" s="98"/>
+      <c r="G55" s="97"/>
       <c r="H55" s="4" t="s">
         <v>64</v>
       </c>
@@ -2934,7 +2921,7 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="95" t="s">
+      <c r="B56" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="29" t="s">
@@ -2944,49 +2931,49 @@
       <c r="E56" s="36"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="83"/>
+      <c r="B57" s="82"/>
       <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G57" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="G57" s="81" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="84"/>
+      <c r="B58" s="83"/>
       <c r="C58" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="G58" s="83"/>
+      <c r="G58" s="82"/>
       <c r="H58" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="97" t="s">
+      <c r="B59" s="96" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
@@ -2994,27 +2981,27 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
-      <c r="G59" s="84"/>
+      <c r="G59" s="83"/>
       <c r="H59" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I59" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="J59" s="7" t="s">
-        <v>178</v>
-      </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="83"/>
+      <c r="B60" s="82"/>
       <c r="C60" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D60" s="72" t="s">
+      <c r="D60" s="71" t="s">
         <v>101</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="G60" s="95" t="s">
+      <c r="G60" s="94" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="29" t="s">
@@ -3024,25 +3011,25 @@
       <c r="J60" s="36"/>
     </row>
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="98"/>
+      <c r="B61" s="97"/>
       <c r="C61" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
-      <c r="G61" s="83"/>
+      <c r="G61" s="82"/>
       <c r="H61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I61" s="64" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="84"/>
+      <c r="G62" s="83"/>
       <c r="H62" s="6" t="s">
         <v>64</v>
       </c>
@@ -3050,7 +3037,7 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="82" t="s">
+      <c r="B63" s="81" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -3058,7 +3045,7 @@
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="13"/>
-      <c r="G63" s="95" t="s">
+      <c r="G63" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="29" t="s">
@@ -3068,33 +3055,33 @@
       <c r="J63" s="36"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="83"/>
+      <c r="B64" s="82"/>
       <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D64" s="64" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="G64" s="83"/>
+      <c r="G64" s="82"/>
       <c r="H64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I64" s="64" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="84"/>
+      <c r="B65" s="83"/>
       <c r="C65" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
-      <c r="G65" s="84"/>
+      <c r="G65" s="83"/>
       <c r="H65" s="6" t="s">
         <v>64</v>
       </c>
@@ -3102,7 +3089,7 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="95" t="s">
+      <c r="B66" s="94" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="29" t="s">
@@ -3110,7 +3097,7 @@
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="36"/>
-      <c r="G66" s="97" t="s">
+      <c r="G66" s="96" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
@@ -3120,31 +3107,31 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="83"/>
+      <c r="B67" s="82"/>
       <c r="C67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-      <c r="G67" s="83"/>
+      <c r="G67" s="82"/>
       <c r="H67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="84"/>
+      <c r="B68" s="83"/>
       <c r="C68" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="G68" s="98"/>
+      <c r="G68" s="97"/>
       <c r="H68" s="4" t="s">
         <v>64</v>
       </c>
@@ -3152,7 +3139,7 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="95" t="s">
+      <c r="B69" s="94" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="29" t="s">
@@ -3162,25 +3149,25 @@
       <c r="E69" s="36"/>
     </row>
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="83"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="64" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G70" s="89" t="s">
+        <v>182</v>
+      </c>
+      <c r="G70" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="H70" s="90"/>
-      <c r="I70" s="90"/>
-      <c r="J70" s="91"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="89"/>
+      <c r="J70" s="90"/>
     </row>
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="84"/>
+      <c r="B71" s="83"/>
       <c r="C71" s="6" t="s">
         <v>64</v>
       </c>
@@ -3188,7 +3175,7 @@
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="95" t="s">
+      <c r="B72" s="94" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="29" t="s">
@@ -3212,7 +3199,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="83"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="2" t="s">
         <v>62</v>
       </c>
@@ -3234,7 +3221,7 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="84"/>
+      <c r="B74" s="83"/>
       <c r="C74" s="6" t="s">
         <v>64</v>
       </c>
@@ -3254,7 +3241,7 @@
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="95" t="s">
+      <c r="B75" s="94" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="29" t="s">
@@ -3274,15 +3261,15 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="83"/>
+      <c r="B76" s="82"/>
       <c r="C76" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G76" s="58"/>
       <c r="H76" s="58"/>
@@ -3290,7 +3277,7 @@
       <c r="J76" s="58"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="84"/>
+      <c r="B77" s="83"/>
       <c r="C77" s="6" t="s">
         <v>64</v>
       </c>
@@ -3310,17 +3297,17 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="97" t="s">
+      <c r="B78" s="96" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D78" s="73" t="s">
-        <v>139</v>
+      <c r="D78" s="72" t="s">
+        <v>137</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>83</v>
@@ -3334,15 +3321,15 @@
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="83"/>
+      <c r="B79" s="82"/>
       <c r="C79" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D79" s="74" t="s">
-        <v>140</v>
+      <c r="D79" s="73" t="s">
+        <v>138</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G79" s="27" t="s">
         <v>84</v>
@@ -3356,15 +3343,15 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="98"/>
+      <c r="B80" s="97"/>
       <c r="C80" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D80" s="75" t="s">
-        <v>138</v>
+      <c r="D80" s="74" t="s">
+        <v>136</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F720A7-BD21-4168-B42F-60C499659235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4087FFB6-A496-4AB5-93BB-BE9DA8EEEDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18150" yWindow="360" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18495" yWindow="705" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,9 +266,6 @@
     <t>Pitch Up/Down</t>
   </si>
   <si>
-    <t>HOTAS - Quick reference -  ENHANCED - T16000 &amp; TWCS Throttle</t>
-  </si>
-  <si>
     <t>TFRP/TFRPHA Rudder</t>
   </si>
   <si>
@@ -627,13 +624,39 @@
   </si>
   <si>
     <t>Dissmiss/Recall Ship</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HOTAS - Quick reference - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ENHANCED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - T16000 &amp; TWCS Throttle</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -643,6 +666,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1493,27 +1524,57 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1524,36 +1585,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1862,17 +1893,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="91" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="93"/>
+      <c r="B2" s="90" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="92"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -1887,18 +1918,18 @@
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="88" t="s">
+      <c r="B4" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="90"/>
-      <c r="G4" s="88" t="s">
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="85"/>
+      <c r="G4" s="83" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="89"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="J4" s="85"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -2107,65 +2138,65 @@
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="77" t="s">
+      <c r="B15" s="93" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="G15" s="81" t="s">
+        <v>106</v>
+      </c>
+      <c r="G15" s="82" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I15" s="66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J15" s="13"/>
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="78"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="78"/>
+      <c r="H16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="67" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="L16" s="9"/>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="89"/>
+      <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="82"/>
-      <c r="H16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="L16" s="9"/>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="79"/>
-      <c r="C17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="65" t="s">
+      <c r="E17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="83"/>
+      <c r="G17" s="79"/>
       <c r="H17" s="6" t="s">
         <v>64</v>
       </c>
@@ -2188,17 +2219,17 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="77" t="s">
+      <c r="B19" s="93" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G19" s="46" t="s">
         <v>28</v>
@@ -2215,119 +2246,119 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="78"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G20" s="84" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="94" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I20" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J20" s="36" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="79"/>
+      <c r="B21" s="89"/>
       <c r="C21" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G21" s="85"/>
+        <v>87</v>
+      </c>
+      <c r="G21" s="95"/>
       <c r="H21" s="15" t="s">
         <v>62</v>
       </c>
       <c r="I21" s="64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="G22" s="86"/>
+      <c r="G22" s="96"/>
       <c r="H22" s="38" t="s">
         <v>64</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J22" s="41" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="77" t="s">
+      <c r="B23" s="93" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D23" s="66" t="s">
+        <v>148</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="G23" s="85" t="s">
+      <c r="G23" s="95" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="39" t="s">
         <v>63</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J23" s="21"/>
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="78"/>
+      <c r="B24" s="86"/>
       <c r="C24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D24" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="G24" s="85"/>
+      <c r="G24" s="95"/>
       <c r="H24" s="15" t="s">
         <v>62</v>
       </c>
       <c r="I24" s="64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J24" s="63"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="79"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
-      <c r="G25" s="87"/>
+      <c r="G25" s="97"/>
       <c r="H25" s="17" t="s">
         <v>64</v>
       </c>
@@ -2340,19 +2371,19 @@
       <c r="I26" s="30"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="93" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="G27" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="G27" s="93" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -2363,44 +2394,44 @@
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="78"/>
+      <c r="B28" s="86"/>
       <c r="C28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D28" s="71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="G28" s="78"/>
+        <v>156</v>
+      </c>
+      <c r="G28" s="86"/>
       <c r="H28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I28" s="67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="79"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="76" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="G29" s="79"/>
+      <c r="G29" s="89"/>
       <c r="H29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J29" s="5"/>
       <c r="L29" s="9"/>
@@ -2411,131 +2442,131 @@
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="G31" s="81" t="s">
+      <c r="G31" s="82" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I31" s="66" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="P31" s="30"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="78"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="19" t="s">
         <v>62</v>
       </c>
       <c r="D32" s="64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" s="20"/>
-      <c r="G32" s="82"/>
+      <c r="G32" s="78"/>
       <c r="H32" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I32" s="64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L32" s="9"/>
       <c r="P32" s="30"/>
     </row>
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="80"/>
+      <c r="B33" s="87"/>
       <c r="C33" s="34" t="s">
         <v>64</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="G33" s="83"/>
+      <c r="G33" s="79"/>
       <c r="H33" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J33" s="7"/>
       <c r="L33" s="9"/>
       <c r="P33" s="30"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="86" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" s="94" t="s">
+      <c r="G34" s="77" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="78"/>
+      <c r="B35" s="86"/>
       <c r="C35" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G35" s="82"/>
+      <c r="G35" s="78"/>
       <c r="H35" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I35" s="64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L35" s="9"/>
       <c r="P35" s="30"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="80"/>
+      <c r="B36" s="87"/>
       <c r="C36" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="83"/>
+      <c r="G36" s="79"/>
       <c r="H36" s="6" t="s">
         <v>64</v>
       </c>
@@ -2546,46 +2577,46 @@
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="88" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="29" t="s">
         <v>63</v>
       </c>
       <c r="D37" s="70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="G37" s="94" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" s="77" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J37" s="36"/>
       <c r="P37" s="30"/>
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="78"/>
+      <c r="B38" s="86"/>
       <c r="C38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D38" s="64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="G38" s="82"/>
+      <c r="G38" s="78"/>
       <c r="H38" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I38" s="64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J38" s="3"/>
       <c r="L38" s="9"/>
@@ -2593,17 +2624,17 @@
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="80"/>
+      <c r="B39" s="87"/>
       <c r="C39" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D39" s="68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="G39" s="83"/>
+        <v>156</v>
+      </c>
+      <c r="G39" s="79"/>
       <c r="H39" s="6" t="s">
         <v>64</v>
       </c>
@@ -2614,64 +2645,64 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="88" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>63</v>
       </c>
       <c r="D40" s="70" t="s">
+        <v>158</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="G40" s="96" t="s">
+      <c r="G40" s="80" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J40" s="20"/>
       <c r="P40" s="30"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="78"/>
+      <c r="B41" s="86"/>
       <c r="C41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D41" s="64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="G41" s="82"/>
+      <c r="G41" s="78"/>
       <c r="H41" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I41" s="64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L41" s="9"/>
       <c r="P41" s="30"/>
     </row>
     <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="79"/>
+      <c r="B42" s="89"/>
       <c r="C42" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D42" s="76" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="G42" s="97"/>
+        <v>94</v>
+      </c>
+      <c r="G42" s="81"/>
       <c r="H42" s="4" t="s">
         <v>64</v>
       </c>
@@ -2686,7 +2717,7 @@
       <c r="P43" s="30"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="81" t="s">
+      <c r="B44" s="82" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2694,62 +2725,62 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
-      <c r="G44" s="81" t="s">
+      <c r="G44" s="82" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I44" s="66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L44" s="9"/>
       <c r="P44" s="30"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="82"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D45" s="64" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="82"/>
+      <c r="G45" s="78"/>
       <c r="H45" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I45" s="64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="83"/>
+      <c r="B46" s="79"/>
       <c r="C46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="G46" s="83"/>
+      <c r="G46" s="79"/>
       <c r="H46" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I46" s="68" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="94" t="s">
+      <c r="B47" s="77" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="29" t="s">
@@ -2757,51 +2788,51 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="36"/>
-      <c r="G47" s="94" t="s">
+      <c r="G47" s="77" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I47" s="69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="82"/>
+      <c r="B48" s="78"/>
       <c r="C48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D48" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G48" s="82"/>
+      <c r="G48" s="78"/>
       <c r="H48" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I48" s="64" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="83"/>
+      <c r="B49" s="79"/>
       <c r="C49" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="G49" s="83"/>
+      <c r="G49" s="79"/>
       <c r="H49" s="6" t="s">
         <v>64</v>
       </c>
@@ -2809,7 +2840,7 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="94" t="s">
+      <c r="B50" s="77" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="29" t="s">
@@ -2817,47 +2848,47 @@
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="36"/>
-      <c r="G50" s="94" t="s">
+      <c r="G50" s="77" t="s">
         <v>38</v>
       </c>
       <c r="H50" s="29" t="s">
         <v>63</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="82"/>
+      <c r="B51" s="78"/>
       <c r="C51" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D51" s="64" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G51" s="82"/>
+        <v>154</v>
+      </c>
+      <c r="G51" s="78"/>
       <c r="H51" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I51" s="64" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="83"/>
+      <c r="B52" s="79"/>
       <c r="C52" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="G52" s="83"/>
+      <c r="G52" s="79"/>
       <c r="H52" s="6" t="s">
         <v>64</v>
       </c>
@@ -2865,7 +2896,7 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="94" t="s">
+      <c r="B53" s="77" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="29" t="s">
@@ -2873,47 +2904,47 @@
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="36"/>
-      <c r="G53" s="96" t="s">
+      <c r="G53" s="80" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
         <v>63</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="82"/>
+      <c r="B54" s="78"/>
       <c r="C54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D54" s="64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G54" s="82"/>
+        <v>160</v>
+      </c>
+      <c r="G54" s="78"/>
       <c r="H54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I54" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="83"/>
+      <c r="B55" s="79"/>
       <c r="C55" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
-      <c r="G55" s="97"/>
+      <c r="G55" s="81"/>
       <c r="H55" s="4" t="s">
         <v>64</v>
       </c>
@@ -2921,7 +2952,7 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="94" t="s">
+      <c r="B56" s="77" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="29" t="s">
@@ -2931,49 +2962,49 @@
       <c r="E56" s="36"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="82"/>
+      <c r="B57" s="78"/>
       <c r="C57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G57" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="G57" s="82" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
         <v>63</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="83"/>
+      <c r="B58" s="79"/>
       <c r="C58" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="G58" s="82"/>
+      <c r="G58" s="78"/>
       <c r="H58" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="96" t="s">
+      <c r="B59" s="80" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
@@ -2981,27 +3012,27 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
-      <c r="G59" s="83"/>
+      <c r="G59" s="79"/>
       <c r="H59" s="6" t="s">
         <v>64</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="82"/>
+      <c r="B60" s="78"/>
       <c r="C60" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="G60" s="94" t="s">
+      <c r="G60" s="77" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="29" t="s">
@@ -3011,25 +3042,25 @@
       <c r="J60" s="36"/>
     </row>
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="97"/>
+      <c r="B61" s="81"/>
       <c r="C61" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
-      <c r="G61" s="82"/>
+      <c r="G61" s="78"/>
       <c r="H61" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I61" s="64" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="83"/>
+      <c r="G62" s="79"/>
       <c r="H62" s="6" t="s">
         <v>64</v>
       </c>
@@ -3037,7 +3068,7 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="81" t="s">
+      <c r="B63" s="82" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -3045,7 +3076,7 @@
       </c>
       <c r="D63" s="62"/>
       <c r="E63" s="13"/>
-      <c r="G63" s="94" t="s">
+      <c r="G63" s="77" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="29" t="s">
@@ -3055,33 +3086,33 @@
       <c r="J63" s="36"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="82"/>
+      <c r="B64" s="78"/>
       <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D64" s="64" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="G64" s="82"/>
+      <c r="G64" s="78"/>
       <c r="H64" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I64" s="64" t="s">
+        <v>144</v>
+      </c>
+      <c r="J64" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J64" s="3" t="s">
-        <v>146</v>
-      </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="83"/>
+      <c r="B65" s="79"/>
       <c r="C65" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
-      <c r="G65" s="83"/>
+      <c r="G65" s="79"/>
       <c r="H65" s="6" t="s">
         <v>64</v>
       </c>
@@ -3089,7 +3120,7 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="94" t="s">
+      <c r="B66" s="77" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="29" t="s">
@@ -3097,7 +3128,7 @@
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="36"/>
-      <c r="G66" s="96" t="s">
+      <c r="G66" s="80" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
@@ -3107,31 +3138,31 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="82"/>
+      <c r="B67" s="78"/>
       <c r="C67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-      <c r="G67" s="82"/>
+      <c r="G67" s="78"/>
       <c r="H67" s="2" t="s">
         <v>62</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="83"/>
+      <c r="B68" s="79"/>
       <c r="C68" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="G68" s="97"/>
+      <c r="G68" s="81"/>
       <c r="H68" s="4" t="s">
         <v>64</v>
       </c>
@@ -3139,7 +3170,7 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="94" t="s">
+      <c r="B69" s="77" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="29" t="s">
@@ -3149,25 +3180,25 @@
       <c r="E69" s="36"/>
     </row>
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="82"/>
+      <c r="B70" s="78"/>
       <c r="C70" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="64" t="s">
+        <v>180</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="88" t="s">
-        <v>77</v>
-      </c>
-      <c r="H70" s="89"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="90"/>
+      <c r="G70" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="H70" s="84"/>
+      <c r="I70" s="84"/>
+      <c r="J70" s="85"/>
     </row>
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="83"/>
+      <c r="B71" s="79"/>
       <c r="C71" s="6" t="s">
         <v>64</v>
       </c>
@@ -3175,14 +3206,14 @@
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="94" t="s">
+      <c r="B72" s="77" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="29" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E72" s="36"/>
       <c r="G72" s="22" t="s">
@@ -3199,16 +3230,16 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="82"/>
+      <c r="B73" s="78"/>
       <c r="C73" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E73" s="3"/>
       <c r="G73" s="28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H73" s="43" t="s">
         <v>65</v>
@@ -3217,20 +3248,20 @@
         <v>56</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="83"/>
+      <c r="B74" s="79"/>
       <c r="C74" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E74" s="7"/>
       <c r="G74" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H74" s="51" t="s">
         <v>65</v>
@@ -3241,7 +3272,7 @@
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="94" t="s">
+      <c r="B75" s="77" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="29" t="s">
@@ -3250,7 +3281,7 @@
       <c r="D75" s="29"/>
       <c r="E75" s="36"/>
       <c r="G75" s="56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H75" s="52" t="s">
         <v>65</v>
@@ -3261,15 +3292,15 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="82"/>
+      <c r="B76" s="78"/>
       <c r="C76" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G76" s="58"/>
       <c r="H76" s="58"/>
@@ -3277,14 +3308,14 @@
       <c r="J76" s="58"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="83"/>
+      <c r="B77" s="79"/>
       <c r="C77" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="7"/>
       <c r="G77" s="57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H77" s="59" t="s">
         <v>65</v>
@@ -3293,24 +3324,24 @@
         <v>56</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="96" t="s">
+      <c r="B78" s="80" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D78" s="72" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G78" s="26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H78" s="60" t="s">
         <v>65</v>
@@ -3321,18 +3352,18 @@
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="82"/>
+      <c r="B79" s="78"/>
       <c r="C79" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D79" s="73" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G79" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H79" s="61" t="s">
         <v>65</v>
@@ -3343,19 +3374,44 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="97"/>
+      <c r="B80" s="81"/>
       <c r="C80" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D80" s="74" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="G44:G46"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B78:B80"/>
@@ -3371,34 +3427,9 @@
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="G70:J70"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="G31:G33"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="40" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4087FFB6-A496-4AB5-93BB-BE9DA8EEEDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EC5E73-4B80-41AE-B00B-AF4DD61E03BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18495" yWindow="705" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1050" yWindow="270" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="196">
   <si>
     <t>H1U</t>
   </si>
@@ -216,12 +216,6 @@
   </si>
   <si>
     <t>DX_XROT_AXIS</t>
-  </si>
-  <si>
-    <t>RESERVED - Shift-UP</t>
-  </si>
-  <si>
-    <t>RESERVED - Shift-DOWN</t>
   </si>
   <si>
     <t>M</t>
@@ -650,6 +644,9 @@
       </rPr>
       <t xml:space="preserve"> - T16000 &amp; TWCS Throttle</t>
     </r>
+  </si>
+  <si>
+    <t>RESERVED</t>
   </si>
 </sst>
 </file>
@@ -1425,9 +1422,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1437,9 +1431,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1522,6 +1513,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1894,7 +1891,7 @@
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="90" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C2" s="91"/>
       <c r="D2" s="91"/>
@@ -1947,8 +1944,8 @@
       <c r="B6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="50" t="s">
-        <v>65</v>
+      <c r="C6" s="48" t="s">
+        <v>63</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>6</v>
@@ -1959,8 +1956,8 @@
       <c r="G6" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H6" s="50" t="s">
-        <v>65</v>
+      <c r="H6" s="48" t="s">
+        <v>63</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>6</v>
@@ -1978,25 +1975,25 @@
         <v>50</v>
       </c>
       <c r="C7" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="73" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G7" s="28" t="s">
         <v>45</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="73" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K7"/>
       <c r="L7"/>
@@ -2007,26 +2004,26 @@
       <c r="B8" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="64" t="s">
+      <c r="C8" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="62" t="s">
         <v>55</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="I8" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="K8"/>
       <c r="L8"/>
@@ -2037,26 +2034,26 @@
       <c r="B9" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="51" t="s">
+      <c r="C9" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D9" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="I9" s="64" t="s">
+      <c r="H9" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="62" t="s">
         <v>58</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K9"/>
       <c r="L9"/>
@@ -2067,8 +2064,8 @@
       <c r="B10" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="52" t="s">
-        <v>65</v>
+      <c r="C10" s="50" t="s">
+        <v>63</v>
       </c>
       <c r="D10" s="4">
         <v>0</v>
@@ -2077,14 +2074,14 @@
       <c r="G10" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="51" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" s="64" t="s">
+      <c r="H10" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="62" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K10"/>
       <c r="L10"/>
@@ -2095,14 +2092,14 @@
       <c r="G11" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="52" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" s="76" t="s">
-        <v>71</v>
+      <c r="H11" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="74" t="s">
+        <v>69</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K11"/>
       <c r="L11"/>
@@ -2111,28 +2108,28 @@
     </row>
     <row r="12" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="54" t="s">
+      <c r="C13" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="53" t="s">
+      <c r="G13" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="H13" s="54" t="s">
+      <c r="H13" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="54" t="s">
+      <c r="I13" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="J13" s="55" t="s">
+      <c r="J13" s="53" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2142,22 +2139,22 @@
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G15" s="82" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="66" t="s">
-        <v>134</v>
+        <v>61</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>132</v>
       </c>
       <c r="J15" s="13"/>
       <c r="L15" s="9"/>
@@ -2165,40 +2162,40 @@
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B16" s="86"/>
       <c r="C16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="64" t="s">
-        <v>105</v>
+        <v>60</v>
+      </c>
+      <c r="D16" s="62" t="s">
+        <v>103</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G16" s="78"/>
       <c r="H16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I16" s="67" t="s">
-        <v>116</v>
+        <v>60</v>
+      </c>
+      <c r="I16" s="65" t="s">
+        <v>114</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="89"/>
       <c r="C17" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="65" t="s">
-        <v>86</v>
+        <v>62</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>84</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G17" s="79"/>
       <c r="H17" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I17" s="37"/>
       <c r="J17" s="41"/>
@@ -2209,13 +2206,13 @@
         <v>27</v>
       </c>
       <c r="H18" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="I18" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="J18" s="45" t="s">
-        <v>72</v>
+        <v>63</v>
+      </c>
+      <c r="I18" s="75" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="44" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2223,87 +2220,83 @@
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="I19" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>73</v>
+      <c r="I19" s="76" t="s">
+        <v>195</v>
+      </c>
+      <c r="J19" s="47" t="s">
+        <v>71</v>
       </c>
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B20" s="86"/>
       <c r="C20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="64" t="s">
-        <v>107</v>
+        <v>60</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>105</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G20" s="94" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I20" s="40" t="s">
+        <v>188</v>
+      </c>
+      <c r="J20" s="36" t="s">
         <v>190</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>192</v>
       </c>
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="89"/>
       <c r="C21" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G21" s="95"/>
       <c r="H21" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="64" t="s">
-        <v>138</v>
+        <v>60</v>
+      </c>
+      <c r="I21" s="62" t="s">
+        <v>136</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
       <c r="G22" s="96"/>
       <c r="H22" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="J22" s="41" t="s">
-        <v>193</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I22" s="37"/>
+      <c r="J22" s="41"/>
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -2311,58 +2304,62 @@
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="66" t="s">
-        <v>148</v>
+        <v>61</v>
+      </c>
+      <c r="D23" s="64" t="s">
+        <v>146</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G23" s="95" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="J23" s="21"/>
+        <v>189</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>191</v>
+      </c>
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="86"/>
       <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="70" t="s">
-        <v>108</v>
+        <v>60</v>
+      </c>
+      <c r="D24" s="68" t="s">
+        <v>106</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G24" s="95"/>
       <c r="H24" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="I24" s="64" t="s">
-        <v>131</v>
-      </c>
-      <c r="J24" s="63"/>
+        <v>60</v>
+      </c>
+      <c r="I24" s="62" t="s">
+        <v>129</v>
+      </c>
+      <c r="J24" s="61"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B25" s="89"/>
       <c r="C25" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
       <c r="G25" s="97"/>
       <c r="H25" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="I25" s="37"/>
+        <v>62</v>
+      </c>
+      <c r="I25" s="37" t="s">
+        <v>137</v>
+      </c>
       <c r="J25" s="18"/>
       <c r="L25" s="9"/>
     </row>
@@ -2375,19 +2372,19 @@
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="66" t="s">
-        <v>90</v>
+        <v>61</v>
+      </c>
+      <c r="D27" s="64" t="s">
+        <v>88</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G27" s="93" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I27" s="31"/>
       <c r="J27" s="13"/>
@@ -2396,42 +2393,42 @@
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="86"/>
       <c r="C28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="71" t="s">
-        <v>91</v>
+        <v>60</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>89</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G28" s="86"/>
       <c r="H28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I28" s="67" t="s">
-        <v>117</v>
+        <v>60</v>
+      </c>
+      <c r="I28" s="65" t="s">
+        <v>115</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="89"/>
       <c r="C29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>110</v>
+        <v>62</v>
+      </c>
+      <c r="D29" s="74" t="s">
+        <v>108</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G29" s="89"/>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I29" s="32" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="J29" s="5"/>
       <c r="L29" s="9"/>
@@ -2446,44 +2443,44 @@
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E31" s="13"/>
       <c r="G31" s="82" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I31" s="66" t="s">
-        <v>118</v>
+        <v>61</v>
+      </c>
+      <c r="I31" s="64" t="s">
+        <v>116</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="P31" s="30"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B32" s="86"/>
       <c r="C32" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="D32" s="64" t="s">
-        <v>92</v>
+        <v>60</v>
+      </c>
+      <c r="D32" s="62" t="s">
+        <v>90</v>
       </c>
       <c r="E32" s="20"/>
       <c r="G32" s="78"/>
       <c r="H32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="64" t="s">
-        <v>127</v>
+        <v>60</v>
+      </c>
+      <c r="I32" s="62" t="s">
+        <v>125</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L32" s="9"/>
       <c r="P32" s="30"/>
@@ -2491,18 +2488,18 @@
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="87"/>
       <c r="C33" s="34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E33" s="35"/>
       <c r="G33" s="79"/>
       <c r="H33" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J33" s="7"/>
       <c r="L33" s="9"/>
@@ -2513,46 +2510,46 @@
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E34" s="20"/>
       <c r="G34" s="77" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J34" s="36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B35" s="86"/>
       <c r="C35" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G35" s="78"/>
       <c r="H35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="64" t="s">
-        <v>128</v>
+        <v>60</v>
+      </c>
+      <c r="I35" s="62" t="s">
+        <v>126</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L35" s="9"/>
       <c r="P35" s="30"/>
@@ -2560,15 +2557,15 @@
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="87"/>
       <c r="C36" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E36" s="7"/>
       <c r="G36" s="79"/>
       <c r="H36" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I36" s="6"/>
       <c r="J36" s="7"/>
@@ -2581,22 +2578,22 @@
         <v>2</v>
       </c>
       <c r="C37" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="70" t="s">
-        <v>112</v>
+        <v>61</v>
+      </c>
+      <c r="D37" s="68" t="s">
+        <v>110</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G37" s="77" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I37" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J37" s="36"/>
       <c r="P37" s="30"/>
@@ -2605,18 +2602,18 @@
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="86"/>
       <c r="C38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D38" s="64" t="s">
-        <v>93</v>
+        <v>60</v>
+      </c>
+      <c r="D38" s="62" t="s">
+        <v>91</v>
       </c>
       <c r="E38" s="3"/>
       <c r="G38" s="78"/>
       <c r="H38" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I38" s="64" t="s">
-        <v>129</v>
+        <v>60</v>
+      </c>
+      <c r="I38" s="62" t="s">
+        <v>127</v>
       </c>
       <c r="J38" s="3"/>
       <c r="L38" s="9"/>
@@ -2626,17 +2623,17 @@
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="87"/>
       <c r="C39" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="D39" s="68" t="s">
-        <v>172</v>
+        <v>62</v>
+      </c>
+      <c r="D39" s="66" t="s">
+        <v>170</v>
       </c>
       <c r="E39" s="35" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G39" s="79"/>
       <c r="H39" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="35"/>
@@ -2649,22 +2646,22 @@
         <v>3</v>
       </c>
       <c r="C40" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="70" t="s">
-        <v>158</v>
+        <v>61</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>156</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G40" s="80" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J40" s="20"/>
       <c r="P40" s="30"/>
@@ -2672,21 +2669,21 @@
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="86"/>
       <c r="C41" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D41" s="64" t="s">
-        <v>113</v>
+        <v>60</v>
+      </c>
+      <c r="D41" s="62" t="s">
+        <v>111</v>
       </c>
       <c r="E41" s="3"/>
       <c r="G41" s="78"/>
       <c r="H41" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I41" s="64" t="s">
-        <v>130</v>
+        <v>60</v>
+      </c>
+      <c r="I41" s="62" t="s">
+        <v>128</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L41" s="9"/>
       <c r="P41" s="30"/>
@@ -2694,17 +2691,17 @@
     <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B42" s="89"/>
       <c r="C42" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" s="76" t="s">
-        <v>157</v>
+        <v>62</v>
+      </c>
+      <c r="D42" s="74" t="s">
+        <v>155</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G42" s="81"/>
       <c r="H42" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="5"/>
@@ -2721,7 +2718,7 @@
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
@@ -2729,13 +2726,13 @@
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I44" s="66" t="s">
-        <v>140</v>
+        <v>61</v>
+      </c>
+      <c r="I44" s="64" t="s">
+        <v>138</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L44" s="9"/>
       <c r="P44" s="30"/>
@@ -2743,40 +2740,40 @@
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="78"/>
       <c r="C45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D45" s="64" t="s">
-        <v>98</v>
+        <v>60</v>
+      </c>
+      <c r="D45" s="62" t="s">
+        <v>96</v>
       </c>
       <c r="E45" s="3"/>
       <c r="G45" s="78"/>
       <c r="H45" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I45" s="64" t="s">
-        <v>121</v>
+        <v>60</v>
+      </c>
+      <c r="I45" s="62" t="s">
+        <v>119</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B46" s="79"/>
       <c r="C46" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
       <c r="G46" s="79"/>
       <c r="H46" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I46" s="68" t="s">
-        <v>141</v>
+        <v>62</v>
+      </c>
+      <c r="I46" s="66" t="s">
+        <v>139</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -2784,7 +2781,7 @@
         <v>15</v>
       </c>
       <c r="C47" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="36"/>
@@ -2792,49 +2789,49 @@
         <v>37</v>
       </c>
       <c r="H47" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="I47" s="69" t="s">
-        <v>142</v>
+        <v>61</v>
+      </c>
+      <c r="I47" s="67" t="s">
+        <v>140</v>
       </c>
       <c r="J47" s="36" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B48" s="78"/>
       <c r="C48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="64" t="s">
-        <v>194</v>
+        <v>60</v>
+      </c>
+      <c r="D48" s="62" t="s">
+        <v>192</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G48" s="78"/>
       <c r="H48" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I48" s="64" t="s">
-        <v>122</v>
+        <v>60</v>
+      </c>
+      <c r="I48" s="62" t="s">
+        <v>120</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="79"/>
       <c r="C49" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
       <c r="G49" s="79"/>
       <c r="H49" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="7"/>
@@ -2844,7 +2841,7 @@
         <v>16</v>
       </c>
       <c r="C50" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="36"/>
@@ -2852,45 +2849,45 @@
         <v>38</v>
       </c>
       <c r="H50" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I50" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="78"/>
       <c r="C51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D51" s="64" t="s">
-        <v>99</v>
+        <v>60</v>
+      </c>
+      <c r="D51" s="62" t="s">
+        <v>97</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G51" s="78"/>
       <c r="H51" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" s="64" t="s">
-        <v>123</v>
+        <v>60</v>
+      </c>
+      <c r="I51" s="62" t="s">
+        <v>121</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="79"/>
       <c r="C52" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
       <c r="G52" s="79"/>
       <c r="H52" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I52" s="6"/>
       <c r="J52" s="7"/>
@@ -2900,7 +2897,7 @@
         <v>17</v>
       </c>
       <c r="C53" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="36"/>
@@ -2908,45 +2905,45 @@
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I53" s="19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="78"/>
       <c r="C54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="64" t="s">
-        <v>153</v>
+        <v>60</v>
+      </c>
+      <c r="D54" s="62" t="s">
+        <v>151</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G54" s="78"/>
       <c r="H54" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="64" t="s">
-        <v>124</v>
+        <v>60</v>
+      </c>
+      <c r="I54" s="62" t="s">
+        <v>122</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B55" s="79"/>
       <c r="C55" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
       <c r="G55" s="81"/>
       <c r="H55" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="5"/>
@@ -2956,7 +2953,7 @@
         <v>18</v>
       </c>
       <c r="C56" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D56" s="29"/>
       <c r="E56" s="36"/>
@@ -2964,43 +2961,43 @@
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="78"/>
       <c r="C57" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G57" s="82" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" s="79"/>
       <c r="C58" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
       <c r="G58" s="78"/>
       <c r="H58" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3008,35 +3005,35 @@
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
       <c r="G59" s="79"/>
       <c r="H59" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I59" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="J59" s="7" t="s">
         <v>173</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B60" s="78"/>
       <c r="C60" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D60" s="71" t="s">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="D60" s="69" t="s">
+        <v>98</v>
       </c>
       <c r="E60" s="3"/>
       <c r="G60" s="77" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I60" s="29"/>
       <c r="J60" s="36"/>
@@ -3044,25 +3041,25 @@
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B61" s="81"/>
       <c r="C61" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="5"/>
       <c r="G61" s="78"/>
       <c r="H61" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I61" s="64" t="s">
-        <v>143</v>
+        <v>60</v>
+      </c>
+      <c r="I61" s="62" t="s">
+        <v>141</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G62" s="79"/>
       <c r="H62" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I62" s="6"/>
       <c r="J62" s="7"/>
@@ -3072,15 +3069,15 @@
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D63" s="62"/>
+        <v>61</v>
+      </c>
+      <c r="D63" s="60"/>
       <c r="E63" s="13"/>
       <c r="G63" s="77" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I63" s="29"/>
       <c r="J63" s="36"/>
@@ -3088,33 +3085,33 @@
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="78"/>
       <c r="C64" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D64" s="64" t="s">
-        <v>179</v>
+        <v>60</v>
+      </c>
+      <c r="D64" s="62" t="s">
+        <v>177</v>
       </c>
       <c r="E64" s="3"/>
       <c r="G64" s="78"/>
       <c r="H64" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I64" s="64" t="s">
-        <v>144</v>
+        <v>60</v>
+      </c>
+      <c r="I64" s="62" t="s">
+        <v>142</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B65" s="79"/>
       <c r="C65" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
       <c r="G65" s="79"/>
       <c r="H65" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I65" s="6"/>
       <c r="J65" s="7"/>
@@ -3124,7 +3121,7 @@
         <v>21</v>
       </c>
       <c r="C66" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="36"/>
@@ -3132,7 +3129,7 @@
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
@@ -3140,31 +3137,31 @@
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="78"/>
       <c r="C67" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
       <c r="G67" s="78"/>
       <c r="H67" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B68" s="79"/>
       <c r="C68" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
       <c r="G68" s="81"/>
       <c r="H68" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="5"/>
@@ -3174,7 +3171,7 @@
         <v>22</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D69" s="29"/>
       <c r="E69" s="36"/>
@@ -3182,16 +3179,16 @@
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B70" s="78"/>
       <c r="C70" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D70" s="64" t="s">
-        <v>180</v>
+        <v>60</v>
+      </c>
+      <c r="D70" s="62" t="s">
+        <v>178</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G70" s="83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H70" s="84"/>
       <c r="I70" s="84"/>
@@ -3200,7 +3197,7 @@
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B71" s="79"/>
       <c r="C71" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="7"/>
@@ -3210,17 +3207,17 @@
         <v>23</v>
       </c>
       <c r="C72" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E72" s="36"/>
       <c r="G72" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H72" s="50" t="s">
-        <v>65</v>
+      <c r="H72" s="48" t="s">
+        <v>63</v>
       </c>
       <c r="I72" s="23" t="s">
         <v>6</v>
@@ -3232,39 +3229,39 @@
     <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B73" s="78"/>
       <c r="C73" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E73" s="3"/>
       <c r="G73" s="28" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H73" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="I73" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="I73" s="62" t="s">
         <v>56</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B74" s="79"/>
       <c r="C74" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E74" s="7"/>
       <c r="G74" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="H74" s="51" t="s">
-        <v>65</v>
+        <v>77</v>
+      </c>
+      <c r="H74" s="49" t="s">
+        <v>63</v>
       </c>
       <c r="I74" s="2">
         <v>0</v>
@@ -3276,15 +3273,15 @@
         <v>24</v>
       </c>
       <c r="C75" s="29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D75" s="29"/>
       <c r="E75" s="36"/>
-      <c r="G75" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="H75" s="52" t="s">
-        <v>65</v>
+      <c r="G75" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="H75" s="50" t="s">
+        <v>63</v>
       </c>
       <c r="I75" s="4">
         <v>0</v>
@@ -3294,37 +3291,37 @@
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B76" s="78"/>
       <c r="C76" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
-      <c r="J76" s="58"/>
+        <v>187</v>
+      </c>
+      <c r="G76" s="56"/>
+      <c r="H76" s="56"/>
+      <c r="I76" s="56"/>
+      <c r="J76" s="56"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B77" s="79"/>
       <c r="C77" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="7"/>
-      <c r="G77" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="H77" s="59" t="s">
-        <v>65</v>
+      <c r="G77" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="H77" s="57" t="s">
+        <v>63</v>
       </c>
       <c r="I77" s="19" t="s">
         <v>56</v>
       </c>
       <c r="J77" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
@@ -3332,19 +3329,19 @@
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D78" s="70" t="s">
+        <v>134</v>
+      </c>
+      <c r="E78" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="G78" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="H78" s="58" t="s">
         <v>63</v>
-      </c>
-      <c r="D78" s="72" t="s">
-        <v>136</v>
-      </c>
-      <c r="E78" s="20" t="s">
-        <v>185</v>
-      </c>
-      <c r="G78" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="H78" s="60" t="s">
-        <v>65</v>
       </c>
       <c r="I78" s="2">
         <v>0</v>
@@ -3354,19 +3351,19 @@
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B79" s="78"/>
       <c r="C79" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D79" s="73" t="s">
-        <v>137</v>
+        <v>60</v>
+      </c>
+      <c r="D79" s="71" t="s">
+        <v>135</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G79" s="27" t="s">
-        <v>83</v>
-      </c>
-      <c r="H79" s="61" t="s">
-        <v>65</v>
+        <v>81</v>
+      </c>
+      <c r="H79" s="59" t="s">
+        <v>63</v>
       </c>
       <c r="I79" s="4">
         <v>0</v>
@@ -3376,13 +3373,13 @@
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B80" s="81"/>
       <c r="C80" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D80" s="74" t="s">
-        <v>135</v>
+        <v>62</v>
+      </c>
+      <c r="D80" s="72" t="s">
+        <v>133</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2EC5E73-4B80-41AE-B00B-AF4DD61E03BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0419320-F175-4115-9287-5DC2578B4615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1050" yWindow="270" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="198">
   <si>
     <t>H1U</t>
   </si>
@@ -647,6 +647,12 @@
   </si>
   <si>
     <t>RESERVED</t>
+  </si>
+  <si>
+    <t>fnStateDump()</t>
+  </si>
+  <si>
+    <t>Statedump banner</t>
   </si>
 </sst>
 </file>
@@ -1521,67 +1527,67 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1890,17 +1896,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="90" t="s">
+      <c r="B2" s="91" t="s">
         <v>194</v>
       </c>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="93"/>
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2"/>
@@ -1915,18 +1921,18 @@
       <c r="O3"/>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="88" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="85"/>
-      <c r="G4" s="83" t="s">
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="90"/>
+      <c r="G4" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="85"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="90"/>
       <c r="K4"/>
       <c r="L4"/>
       <c r="M4"/>
@@ -2135,7 +2141,7 @@
     </row>
     <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="77" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -2147,7 +2153,7 @@
       <c r="E15" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="82" t="s">
+      <c r="G15" s="81" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="11" t="s">
@@ -2160,7 +2166,7 @@
       <c r="L15" s="9"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="86"/>
+      <c r="B16" s="78"/>
       <c r="C16" s="2" t="s">
         <v>60</v>
       </c>
@@ -2170,7 +2176,7 @@
       <c r="E16" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="78"/>
+      <c r="G16" s="82"/>
       <c r="H16" s="2" t="s">
         <v>60</v>
       </c>
@@ -2183,7 +2189,7 @@
       <c r="L16" s="9"/>
     </row>
     <row r="17" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="89"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="4" t="s">
         <v>62</v>
       </c>
@@ -2193,7 +2199,7 @@
       <c r="E17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="79"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="6" t="s">
         <v>62</v>
       </c>
@@ -2216,7 +2222,7 @@
       </c>
     </row>
     <row r="19" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="93" t="s">
+      <c r="B19" s="77" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -2243,7 +2249,7 @@
       <c r="L19" s="9"/>
     </row>
     <row r="20" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="86"/>
+      <c r="B20" s="78"/>
       <c r="C20" s="2" t="s">
         <v>60</v>
       </c>
@@ -2253,7 +2259,7 @@
       <c r="E20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="94" t="s">
+      <c r="G20" s="84" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="29" t="s">
@@ -2268,7 +2274,7 @@
       <c r="L20" s="9"/>
     </row>
     <row r="21" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="89"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="4" t="s">
         <v>62</v>
       </c>
@@ -2278,7 +2284,7 @@
       <c r="E21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="95"/>
+      <c r="G21" s="85"/>
       <c r="H21" s="15" t="s">
         <v>60</v>
       </c>
@@ -2291,7 +2297,7 @@
     </row>
     <row r="22" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9"/>
-      <c r="G22" s="96"/>
+      <c r="G22" s="86"/>
       <c r="H22" s="38" t="s">
         <v>62</v>
       </c>
@@ -2300,7 +2306,7 @@
       <c r="L22" s="9"/>
     </row>
     <row r="23" spans="2:16" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="77" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -2312,7 +2318,7 @@
       <c r="E23" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="95" t="s">
+      <c r="G23" s="85" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="39" t="s">
@@ -2327,7 +2333,7 @@
       <c r="L23" s="9"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B24" s="86"/>
+      <c r="B24" s="78"/>
       <c r="C24" s="2" t="s">
         <v>60</v>
       </c>
@@ -2337,7 +2343,7 @@
       <c r="E24" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="95"/>
+      <c r="G24" s="85"/>
       <c r="H24" s="15" t="s">
         <v>60</v>
       </c>
@@ -2347,13 +2353,13 @@
       <c r="J24" s="61"/>
     </row>
     <row r="25" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="89"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="5"/>
-      <c r="G25" s="97"/>
+      <c r="G25" s="87"/>
       <c r="H25" s="17" t="s">
         <v>62</v>
       </c>
@@ -2368,7 +2374,7 @@
       <c r="I26" s="30"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B27" s="93" t="s">
+      <c r="B27" s="77" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -2380,7 +2386,7 @@
       <c r="E27" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G27" s="93" t="s">
+      <c r="G27" s="77" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="11" t="s">
@@ -2391,7 +2397,7 @@
       <c r="L27" s="9"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="86"/>
+      <c r="B28" s="78"/>
       <c r="C28" s="2" t="s">
         <v>60</v>
       </c>
@@ -2401,7 +2407,7 @@
       <c r="E28" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="G28" s="86"/>
+      <c r="G28" s="78"/>
       <c r="H28" s="2" t="s">
         <v>60</v>
       </c>
@@ -2413,7 +2419,7 @@
       </c>
     </row>
     <row r="29" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="89"/>
+      <c r="B29" s="79"/>
       <c r="C29" s="4" t="s">
         <v>62</v>
       </c>
@@ -2423,7 +2429,7 @@
       <c r="E29" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G29" s="89"/>
+      <c r="G29" s="79"/>
       <c r="H29" s="4" t="s">
         <v>62</v>
       </c>
@@ -2439,7 +2445,7 @@
       <c r="L30" s="9"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="93" t="s">
+      <c r="B31" s="77" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -2449,7 +2455,7 @@
         <v>102</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="G31" s="82" t="s">
+      <c r="G31" s="81" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="11" t="s">
@@ -2464,7 +2470,7 @@
       <c r="P31" s="30"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="86"/>
+      <c r="B32" s="78"/>
       <c r="C32" s="19" t="s">
         <v>60</v>
       </c>
@@ -2472,7 +2478,7 @@
         <v>90</v>
       </c>
       <c r="E32" s="20"/>
-      <c r="G32" s="78"/>
+      <c r="G32" s="82"/>
       <c r="H32" s="2" t="s">
         <v>60</v>
       </c>
@@ -2486,7 +2492,7 @@
       <c r="P32" s="30"/>
     </row>
     <row r="33" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="87"/>
+      <c r="B33" s="80"/>
       <c r="C33" s="34" t="s">
         <v>62</v>
       </c>
@@ -2494,7 +2500,7 @@
         <v>95</v>
       </c>
       <c r="E33" s="35"/>
-      <c r="G33" s="79"/>
+      <c r="G33" s="83"/>
       <c r="H33" s="6" t="s">
         <v>62</v>
       </c>
@@ -2506,7 +2512,7 @@
       <c r="P33" s="30"/>
     </row>
     <row r="34" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="78" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="19" t="s">
@@ -2516,7 +2522,7 @@
         <v>94</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" s="77" t="s">
+      <c r="G34" s="94" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="29" t="s">
@@ -2531,7 +2537,7 @@
       <c r="P34" s="30"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B35" s="86"/>
+      <c r="B35" s="78"/>
       <c r="C35" s="2" t="s">
         <v>60</v>
       </c>
@@ -2541,7 +2547,7 @@
       <c r="E35" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="78"/>
+      <c r="G35" s="82"/>
       <c r="H35" s="2" t="s">
         <v>60</v>
       </c>
@@ -2555,7 +2561,7 @@
       <c r="P35" s="30"/>
     </row>
     <row r="36" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="87"/>
+      <c r="B36" s="80"/>
       <c r="C36" s="6" t="s">
         <v>62</v>
       </c>
@@ -2563,7 +2569,7 @@
         <v>93</v>
       </c>
       <c r="E36" s="7"/>
-      <c r="G36" s="79"/>
+      <c r="G36" s="83"/>
       <c r="H36" s="6" t="s">
         <v>62</v>
       </c>
@@ -2574,7 +2580,7 @@
       <c r="Q36" s="8"/>
     </row>
     <row r="37" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="88" t="s">
+      <c r="B37" s="95" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="29" t="s">
@@ -2586,7 +2592,7 @@
       <c r="E37" s="36" t="s">
         <v>154</v>
       </c>
-      <c r="G37" s="77" t="s">
+      <c r="G37" s="94" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="29" t="s">
@@ -2600,7 +2606,7 @@
       <c r="Q37" s="8"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B38" s="86"/>
+      <c r="B38" s="78"/>
       <c r="C38" s="2" t="s">
         <v>60</v>
       </c>
@@ -2608,7 +2614,7 @@
         <v>91</v>
       </c>
       <c r="E38" s="3"/>
-      <c r="G38" s="78"/>
+      <c r="G38" s="82"/>
       <c r="H38" s="2" t="s">
         <v>60</v>
       </c>
@@ -2621,7 +2627,7 @@
       <c r="Q38" s="8"/>
     </row>
     <row r="39" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="87"/>
+      <c r="B39" s="80"/>
       <c r="C39" s="6" t="s">
         <v>62</v>
       </c>
@@ -2631,7 +2637,7 @@
       <c r="E39" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="G39" s="79"/>
+      <c r="G39" s="83"/>
       <c r="H39" s="6" t="s">
         <v>62</v>
       </c>
@@ -2642,7 +2648,7 @@
       <c r="Q39" s="8"/>
     </row>
     <row r="40" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="95" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="29" t="s">
@@ -2654,7 +2660,7 @@
       <c r="E40" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G40" s="80" t="s">
+      <c r="G40" s="96" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="19" t="s">
@@ -2667,7 +2673,7 @@
       <c r="P40" s="30"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B41" s="86"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="2" t="s">
         <v>60</v>
       </c>
@@ -2675,7 +2681,7 @@
         <v>111</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="G41" s="78"/>
+      <c r="G41" s="82"/>
       <c r="H41" s="2" t="s">
         <v>60</v>
       </c>
@@ -2689,7 +2695,7 @@
       <c r="P41" s="30"/>
     </row>
     <row r="42" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="89"/>
+      <c r="B42" s="79"/>
       <c r="C42" s="4" t="s">
         <v>62</v>
       </c>
@@ -2699,7 +2705,7 @@
       <c r="E42" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G42" s="81"/>
+      <c r="G42" s="97"/>
       <c r="H42" s="4" t="s">
         <v>62</v>
       </c>
@@ -2714,7 +2720,7 @@
       <c r="P43" s="30"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B44" s="82" t="s">
+      <c r="B44" s="81" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2722,7 +2728,7 @@
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="13"/>
-      <c r="G44" s="82" t="s">
+      <c r="G44" s="81" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="11" t="s">
@@ -2738,7 +2744,7 @@
       <c r="P44" s="30"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B45" s="78"/>
+      <c r="B45" s="82"/>
       <c r="C45" s="2" t="s">
         <v>60</v>
       </c>
@@ -2746,7 +2752,7 @@
         <v>96</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="G45" s="78"/>
+      <c r="G45" s="82"/>
       <c r="H45" s="2" t="s">
         <v>60</v>
       </c>
@@ -2759,13 +2765,13 @@
       <c r="L45" s="9"/>
     </row>
     <row r="46" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="79"/>
+      <c r="B46" s="83"/>
       <c r="C46" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="7"/>
-      <c r="G46" s="79"/>
+      <c r="G46" s="83"/>
       <c r="H46" s="6" t="s">
         <v>62</v>
       </c>
@@ -2777,7 +2783,7 @@
       </c>
     </row>
     <row r="47" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="77" t="s">
+      <c r="B47" s="94" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="29" t="s">
@@ -2785,7 +2791,7 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="36"/>
-      <c r="G47" s="77" t="s">
+      <c r="G47" s="94" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="29" t="s">
@@ -2800,7 +2806,7 @@
       <c r="L47" s="9"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B48" s="78"/>
+      <c r="B48" s="82"/>
       <c r="C48" s="2" t="s">
         <v>60</v>
       </c>
@@ -2810,7 +2816,7 @@
       <c r="E48" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G48" s="78"/>
+      <c r="G48" s="82"/>
       <c r="H48" s="2" t="s">
         <v>60</v>
       </c>
@@ -2823,13 +2829,13 @@
       <c r="L48" s="9"/>
     </row>
     <row r="49" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="79"/>
+      <c r="B49" s="83"/>
       <c r="C49" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="G49" s="79"/>
+      <c r="G49" s="83"/>
       <c r="H49" s="6" t="s">
         <v>62</v>
       </c>
@@ -2837,7 +2843,7 @@
       <c r="J49" s="7"/>
     </row>
     <row r="50" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="77" t="s">
+      <c r="B50" s="94" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="29" t="s">
@@ -2845,7 +2851,7 @@
       </c>
       <c r="D50" s="29"/>
       <c r="E50" s="36"/>
-      <c r="G50" s="77" t="s">
+      <c r="G50" s="94" t="s">
         <v>38</v>
       </c>
       <c r="H50" s="29" t="s">
@@ -2857,7 +2863,7 @@
       <c r="J50" s="36"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="78"/>
+      <c r="B51" s="82"/>
       <c r="C51" s="2" t="s">
         <v>60</v>
       </c>
@@ -2867,7 +2873,7 @@
       <c r="E51" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G51" s="78"/>
+      <c r="G51" s="82"/>
       <c r="H51" s="2" t="s">
         <v>60</v>
       </c>
@@ -2879,13 +2885,13 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="79"/>
+      <c r="B52" s="83"/>
       <c r="C52" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="7"/>
-      <c r="G52" s="79"/>
+      <c r="G52" s="83"/>
       <c r="H52" s="6" t="s">
         <v>62</v>
       </c>
@@ -2893,7 +2899,7 @@
       <c r="J52" s="7"/>
     </row>
     <row r="53" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="77" t="s">
+      <c r="B53" s="94" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="29" t="s">
@@ -2901,7 +2907,7 @@
       </c>
       <c r="D53" s="29"/>
       <c r="E53" s="36"/>
-      <c r="G53" s="80" t="s">
+      <c r="G53" s="96" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="19" t="s">
@@ -2913,7 +2919,7 @@
       <c r="J53" s="20"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="78"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="2" t="s">
         <v>60</v>
       </c>
@@ -2923,7 +2929,7 @@
       <c r="E54" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G54" s="78"/>
+      <c r="G54" s="82"/>
       <c r="H54" s="2" t="s">
         <v>60</v>
       </c>
@@ -2935,13 +2941,13 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="79"/>
+      <c r="B55" s="83"/>
       <c r="C55" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="7"/>
-      <c r="G55" s="81"/>
+      <c r="G55" s="97"/>
       <c r="H55" s="4" t="s">
         <v>62</v>
       </c>
@@ -2949,7 +2955,7 @@
       <c r="J55" s="5"/>
     </row>
     <row r="56" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="77" t="s">
+      <c r="B56" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="29" t="s">
@@ -2959,7 +2965,7 @@
       <c r="E56" s="36"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="78"/>
+      <c r="B57" s="82"/>
       <c r="C57" s="2" t="s">
         <v>60</v>
       </c>
@@ -2969,7 +2975,7 @@
       <c r="E57" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G57" s="82" t="s">
+      <c r="G57" s="81" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="11" t="s">
@@ -2983,13 +2989,13 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="79"/>
+      <c r="B58" s="83"/>
       <c r="C58" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="7"/>
-      <c r="G58" s="78"/>
+      <c r="G58" s="82"/>
       <c r="H58" s="2" t="s">
         <v>60</v>
       </c>
@@ -3001,7 +3007,7 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="80" t="s">
+      <c r="B59" s="96" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="19" t="s">
@@ -3009,7 +3015,7 @@
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="20"/>
-      <c r="G59" s="79"/>
+      <c r="G59" s="83"/>
       <c r="H59" s="6" t="s">
         <v>62</v>
       </c>
@@ -3021,7 +3027,7 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="78"/>
+      <c r="B60" s="82"/>
       <c r="C60" s="2" t="s">
         <v>60</v>
       </c>
@@ -3029,7 +3035,7 @@
         <v>98</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="G60" s="77" t="s">
+      <c r="G60" s="94" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="29" t="s">
@@ -3039,13 +3045,17 @@
       <c r="J60" s="36"/>
     </row>
     <row r="61" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="81"/>
+      <c r="B61" s="97"/>
       <c r="C61" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="5"/>
-      <c r="G61" s="78"/>
+      <c r="D61" s="74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G61" s="82"/>
       <c r="H61" s="2" t="s">
         <v>60</v>
       </c>
@@ -3057,7 +3067,7 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G62" s="79"/>
+      <c r="G62" s="83"/>
       <c r="H62" s="6" t="s">
         <v>62</v>
       </c>
@@ -3065,7 +3075,7 @@
       <c r="J62" s="7"/>
     </row>
     <row r="63" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="82" t="s">
+      <c r="B63" s="81" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -3073,7 +3083,7 @@
       </c>
       <c r="D63" s="60"/>
       <c r="E63" s="13"/>
-      <c r="G63" s="77" t="s">
+      <c r="G63" s="94" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="29" t="s">
@@ -3083,7 +3093,7 @@
       <c r="J63" s="36"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="78"/>
+      <c r="B64" s="82"/>
       <c r="C64" s="2" t="s">
         <v>60</v>
       </c>
@@ -3091,7 +3101,7 @@
         <v>177</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="G64" s="78"/>
+      <c r="G64" s="82"/>
       <c r="H64" s="2" t="s">
         <v>60</v>
       </c>
@@ -3103,13 +3113,13 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="79"/>
+      <c r="B65" s="83"/>
       <c r="C65" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="7"/>
-      <c r="G65" s="79"/>
+      <c r="G65" s="83"/>
       <c r="H65" s="6" t="s">
         <v>62</v>
       </c>
@@ -3117,7 +3127,7 @@
       <c r="J65" s="7"/>
     </row>
     <row r="66" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="77" t="s">
+      <c r="B66" s="94" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="29" t="s">
@@ -3125,7 +3135,7 @@
       </c>
       <c r="D66" s="29"/>
       <c r="E66" s="36"/>
-      <c r="G66" s="80" t="s">
+      <c r="G66" s="96" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="19" t="s">
@@ -3135,13 +3145,13 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="78"/>
+      <c r="B67" s="82"/>
       <c r="C67" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-      <c r="G67" s="78"/>
+      <c r="G67" s="82"/>
       <c r="H67" s="2" t="s">
         <v>60</v>
       </c>
@@ -3153,13 +3163,13 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="79"/>
+      <c r="B68" s="83"/>
       <c r="C68" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="7"/>
-      <c r="G68" s="81"/>
+      <c r="G68" s="97"/>
       <c r="H68" s="4" t="s">
         <v>62</v>
       </c>
@@ -3167,7 +3177,7 @@
       <c r="J68" s="5"/>
     </row>
     <row r="69" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="77" t="s">
+      <c r="B69" s="94" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="29" t="s">
@@ -3177,7 +3187,7 @@
       <c r="E69" s="36"/>
     </row>
     <row r="70" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="78"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="2" t="s">
         <v>60</v>
       </c>
@@ -3187,15 +3197,15 @@
       <c r="E70" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G70" s="83" t="s">
+      <c r="G70" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="H70" s="84"/>
-      <c r="I70" s="84"/>
-      <c r="J70" s="85"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="89"/>
+      <c r="J70" s="90"/>
     </row>
     <row r="71" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="79"/>
+      <c r="B71" s="83"/>
       <c r="C71" s="6" t="s">
         <v>62</v>
       </c>
@@ -3203,7 +3213,7 @@
       <c r="E71" s="7"/>
     </row>
     <row r="72" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="77" t="s">
+      <c r="B72" s="94" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="29" t="s">
@@ -3227,7 +3237,7 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="78"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="2" t="s">
         <v>60</v>
       </c>
@@ -3249,7 +3259,7 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="79"/>
+      <c r="B74" s="83"/>
       <c r="C74" s="6" t="s">
         <v>62</v>
       </c>
@@ -3269,7 +3279,7 @@
       <c r="J74" s="3"/>
     </row>
     <row r="75" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="77" t="s">
+      <c r="B75" s="94" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="29" t="s">
@@ -3289,7 +3299,7 @@
       <c r="J75" s="5"/>
     </row>
     <row r="76" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="78"/>
+      <c r="B76" s="82"/>
       <c r="C76" s="2" t="s">
         <v>60</v>
       </c>
@@ -3305,7 +3315,7 @@
       <c r="J76" s="56"/>
     </row>
     <row r="77" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="79"/>
+      <c r="B77" s="83"/>
       <c r="C77" s="6" t="s">
         <v>62</v>
       </c>
@@ -3325,7 +3335,7 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="80" t="s">
+      <c r="B78" s="96" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="19" t="s">
@@ -3349,7 +3359,7 @@
       <c r="J78" s="3"/>
     </row>
     <row r="79" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="78"/>
+      <c r="B79" s="82"/>
       <c r="C79" s="2" t="s">
         <v>60</v>
       </c>
@@ -3371,7 +3381,7 @@
       <c r="J79" s="5"/>
     </row>
     <row r="80" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="81"/>
+      <c r="B80" s="97"/>
       <c r="C80" s="4" t="s">
         <v>62</v>
       </c>
@@ -3384,31 +3394,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G44:G46"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B78:B80"/>
@@ -3424,6 +3409,31 @@
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G31:G33"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>

--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0419320-F175-4115-9287-5DC2578B4615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A637BBD-1EE3-478F-B05C-EFF523148743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1050" yWindow="270" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1395" yWindow="615" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3435,11 +3435,7 @@
     <mergeCell ref="G27:G29"/>
     <mergeCell ref="G31:G33"/>
   </mergeCells>
-  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="93" fitToHeight="0" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
--- a/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
+++ b/MapFiles/HOTAS Switch and Button - Quick Reference - ENHANCED - T16000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_T16000\MapFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thrustmaster\ED_TargetScript_T16000\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1C428E-2522-4798-9721-0D55D1933A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039DE640-BB8A-4B88-A3D1-9AD93E4B1C9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17445" yWindow="615" windowWidth="19725" windowHeight="20235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8775" yWindow="3135" windowWidth="23175" windowHeight="16815" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="211">
   <si>
     <t>H1U</t>
   </si>
@@ -615,9 +615,6 @@
   </si>
   <si>
     <t>fnDRSHIP()</t>
-  </si>
-  <si>
-    <t>Dissmiss/Recall Ship</t>
   </si>
   <si>
     <t>RESERVED</t>
@@ -653,6 +650,48 @@
       </rPr>
       <t xml:space="preserve"> - T16000 &amp; TWCS Throttle</t>
     </r>
+  </si>
+  <si>
+    <t>Deploy/Recover SRV</t>
+  </si>
+  <si>
+    <t>fnDeploySRV()</t>
+  </si>
+  <si>
+    <t>Dismiss/Recall Ship</t>
+  </si>
+  <si>
+    <t>fnDeployFighter()</t>
+  </si>
+  <si>
+    <t>Deploy/Recover fighter</t>
+  </si>
+  <si>
+    <t>fnDEBUG()</t>
+  </si>
+  <si>
+    <t>Run debug code</t>
+  </si>
+  <si>
+    <t>fnSetOriginStation()</t>
+  </si>
+  <si>
+    <t>Connection status</t>
+  </si>
+  <si>
+    <t>Set origin for Timer</t>
+  </si>
+  <si>
+    <t>m_ClearChatBox</t>
+  </si>
+  <si>
+    <t>Clears the chat box</t>
+  </si>
+  <si>
+    <t>tgTxt2Speech()</t>
+  </si>
+  <si>
+    <t>TTS OFF/ON</t>
   </si>
 </sst>
 </file>
@@ -715,7 +754,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="41">
     <border>
       <left/>
       <right/>
@@ -1275,24 +1314,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1466,13 +1492,88 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1480,111 +1581,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1892,17 +1888,17 @@
   <sheetData>
     <row r="1" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="72" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="74"/>
+      <c r="B2" s="82" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="84"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
@@ -1917,18 +1913,18 @@
       <c r="O3" s="2"/>
     </row>
     <row r="4" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="67"/>
-      <c r="G4" s="65" t="s">
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="81"/>
+      <c r="G4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="66"/>
-      <c r="I4" s="66"/>
-      <c r="J4" s="67"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="81"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1979,7 +1975,7 @@
       <c r="C7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="80" t="s">
+      <c r="D7" s="59" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -1991,7 +1987,7 @@
       <c r="H7" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I7" s="80" t="s">
+      <c r="I7" s="59" t="s">
         <v>57</v>
       </c>
       <c r="J7" s="12" t="s">
@@ -2009,7 +2005,7 @@
       <c r="C8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="24" t="s">
         <v>55</v>
       </c>
       <c r="E8" s="15" t="s">
@@ -2021,7 +2017,7 @@
       <c r="H8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="81" t="s">
+      <c r="I8" s="24" t="s">
         <v>56</v>
       </c>
       <c r="J8" s="15" t="s">
@@ -2039,7 +2035,7 @@
       <c r="C9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="24" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="15" t="s">
@@ -2051,7 +2047,7 @@
       <c r="H9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="81" t="s">
+      <c r="I9" s="24" t="s">
         <v>58</v>
       </c>
       <c r="J9" s="15" t="s">
@@ -2069,7 +2065,7 @@
       <c r="C10" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="82">
+      <c r="D10" s="19">
         <v>0</v>
       </c>
       <c r="E10" s="20"/>
@@ -2079,7 +2075,7 @@
       <c r="H10" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="81" t="s">
+      <c r="I10" s="24" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="15" t="s">
@@ -2091,14 +2087,13 @@
       <c r="O10" s="2"/>
     </row>
     <row r="11" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D11" s="83"/>
       <c r="G11" s="17" t="s">
         <v>49</v>
       </c>
       <c r="H11" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="I11" s="82" t="s">
+      <c r="I11" s="19" t="s">
         <v>69</v>
       </c>
       <c r="J11" s="20" t="s">
@@ -2109,10 +2104,7 @@
       <c r="M11" s="2"/>
       <c r="O11" s="2"/>
     </row>
-    <row r="12" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D12" s="83"/>
-      <c r="I12" s="83"/>
-    </row>
+    <row r="12" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>4</v>
@@ -2120,7 +2112,7 @@
       <c r="C13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="84" t="s">
+      <c r="D13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -2132,58 +2124,55 @@
       <c r="H13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I13" s="84" t="s">
+      <c r="I13" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D14" s="83"/>
-      <c r="I14" s="83"/>
-    </row>
+    <row r="14" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="68" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="85" t="s">
+      <c r="D15" s="21" t="s">
         <v>82</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="72" t="s">
         <v>26</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="85" t="s">
+      <c r="I15" s="21" t="s">
         <v>132</v>
       </c>
       <c r="J15" s="22"/>
       <c r="L15" s="23"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B16" s="68"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="81" t="s">
+      <c r="D16" s="24" t="s">
         <v>103</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G16" s="60"/>
+      <c r="G16" s="73"/>
       <c r="H16" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="92" t="s">
+      <c r="I16" s="62" t="s">
         <v>114</v>
       </c>
       <c r="J16" s="25" t="s">
@@ -2192,17 +2181,17 @@
       <c r="L16" s="23"/>
     </row>
     <row r="17" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="71"/>
+      <c r="B17" s="70"/>
       <c r="C17" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="86" t="s">
+      <c r="D17" s="60" t="s">
         <v>84</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="61"/>
+      <c r="G17" s="74"/>
       <c r="H17" s="26" t="s">
         <v>62</v>
       </c>
@@ -2211,7 +2200,6 @@
       <c r="L17" s="23"/>
     </row>
     <row r="18" spans="2:16" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D18" s="83"/>
       <c r="G18" s="29" t="s">
         <v>27</v>
       </c>
@@ -2219,20 +2207,20 @@
         <v>63</v>
       </c>
       <c r="I18" s="30" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J18" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="68" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="21" t="s">
         <v>86</v>
       </c>
       <c r="E19" s="22" t="s">
@@ -2245,7 +2233,7 @@
         <v>63</v>
       </c>
       <c r="I19" s="34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J19" s="35" t="s">
         <v>71</v>
@@ -2253,23 +2241,23 @@
       <c r="L19" s="23"/>
     </row>
     <row r="20" spans="2:16" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="68"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="81" t="s">
+      <c r="D20" s="24" t="s">
         <v>105</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="76" t="s">
+      <c r="G20" s="75" t="s">
         <v>29</v>
       </c>
       <c r="H20" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I20" s="93" t="s">
+      <c r="I20" s="63" t="s">
         <v>188</v>
       </c>
       <c r="J20" s="37" t="s">
@@ -2278,21 +2266,21 @@
       <c r="L20" s="23"/>
     </row>
     <row r="21" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="71"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D21" s="60" t="s">
         <v>87</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="77"/>
+      <c r="G21" s="76"/>
       <c r="H21" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I21" s="81" t="s">
+      <c r="I21" s="24" t="s">
         <v>136</v>
       </c>
       <c r="J21" s="25" t="s">
@@ -2301,35 +2289,38 @@
     </row>
     <row r="22" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="23"/>
-      <c r="D22" s="83"/>
-      <c r="G22" s="78"/>
+      <c r="G22" s="77"/>
       <c r="H22" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="94"/>
-      <c r="J22" s="28"/>
+      <c r="I22" s="64" t="s">
+        <v>209</v>
+      </c>
+      <c r="J22" s="28" t="s">
+        <v>210</v>
+      </c>
       <c r="L22" s="23"/>
     </row>
     <row r="23" spans="2:16" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D23" s="85" t="s">
+      <c r="D23" s="21" t="s">
         <v>146</v>
       </c>
       <c r="E23" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="G23" s="77" t="s">
+      <c r="G23" s="76" t="s">
         <v>30</v>
       </c>
       <c r="H23" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="I23" s="95" t="s">
+      <c r="I23" s="65" t="s">
         <v>189</v>
       </c>
       <c r="J23" s="41" t="s">
@@ -2338,37 +2329,37 @@
       <c r="L23" s="23"/>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B24" s="68"/>
+      <c r="B24" s="69"/>
       <c r="C24" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D24" s="87" t="s">
+      <c r="D24" s="48" t="s">
         <v>106</v>
       </c>
       <c r="E24" s="42" t="s">
         <v>107</v>
       </c>
-      <c r="G24" s="77"/>
+      <c r="G24" s="76"/>
       <c r="H24" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="I24" s="81" t="s">
+      <c r="I24" s="24" t="s">
         <v>129</v>
       </c>
       <c r="J24" s="43"/>
     </row>
     <row r="25" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="71"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="82"/>
+      <c r="D25" s="19"/>
       <c r="E25" s="20"/>
-      <c r="G25" s="79"/>
+      <c r="G25" s="78"/>
       <c r="H25" s="44" t="s">
         <v>62</v>
       </c>
-      <c r="I25" s="94" t="s">
+      <c r="I25" s="64" t="s">
         <v>137</v>
       </c>
       <c r="J25" s="45"/>
@@ -2376,48 +2367,47 @@
     </row>
     <row r="26" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B26" s="23"/>
-      <c r="D26" s="83"/>
-      <c r="I26" s="96"/>
+      <c r="I26" s="46"/>
     </row>
     <row r="27" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="68" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D27" s="85" t="s">
+      <c r="D27" s="21" t="s">
         <v>88</v>
       </c>
       <c r="E27" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="G27" s="75" t="s">
+      <c r="G27" s="68" t="s">
         <v>31</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I27" s="97"/>
+      <c r="I27" s="66"/>
       <c r="J27" s="22"/>
       <c r="L27" s="23"/>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B28" s="68"/>
+      <c r="B28" s="69"/>
       <c r="C28" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D28" s="88" t="s">
+      <c r="D28" s="61" t="s">
         <v>89</v>
       </c>
       <c r="E28" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="G28" s="68"/>
+      <c r="G28" s="69"/>
       <c r="H28" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I28" s="92" t="s">
+      <c r="I28" s="62" t="s">
         <v>115</v>
       </c>
       <c r="J28" s="15" t="s">
@@ -2425,50 +2415,49 @@
       </c>
     </row>
     <row r="29" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="71"/>
+      <c r="B29" s="70"/>
       <c r="C29" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="82" t="s">
+      <c r="D29" s="19" t="s">
         <v>108</v>
       </c>
       <c r="E29" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="G29" s="71"/>
+      <c r="G29" s="70"/>
       <c r="H29" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="98" t="s">
+      <c r="I29" s="67" t="s">
         <v>148</v>
       </c>
       <c r="J29" s="20"/>
       <c r="L29" s="23"/>
     </row>
     <row r="30" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="83"/>
       <c r="G30" s="47"/>
-      <c r="I30" s="96"/>
+      <c r="I30" s="46"/>
       <c r="L30" s="23"/>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="68" t="s">
         <v>0</v>
       </c>
       <c r="C31" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="85" t="s">
+      <c r="D31" s="21" t="s">
         <v>102</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="72" t="s">
         <v>32</v>
       </c>
       <c r="H31" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I31" s="85" t="s">
+      <c r="I31" s="21" t="s">
         <v>116</v>
       </c>
       <c r="J31" s="22" t="s">
@@ -2477,19 +2466,19 @@
       <c r="P31" s="46"/>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B32" s="68"/>
+      <c r="B32" s="69"/>
       <c r="C32" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="D32" s="81" t="s">
+      <c r="D32" s="24" t="s">
         <v>90</v>
       </c>
       <c r="E32" s="42"/>
-      <c r="G32" s="60"/>
+      <c r="G32" s="73"/>
       <c r="H32" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I32" s="81" t="s">
+      <c r="I32" s="24" t="s">
         <v>125</v>
       </c>
       <c r="J32" s="15" t="s">
@@ -2499,19 +2488,19 @@
       <c r="P32" s="46"/>
     </row>
     <row r="33" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="69"/>
+      <c r="B33" s="71"/>
       <c r="C33" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="D33" s="89" t="s">
+      <c r="D33" s="26" t="s">
         <v>95</v>
       </c>
       <c r="E33" s="50"/>
-      <c r="G33" s="61"/>
+      <c r="G33" s="74"/>
       <c r="H33" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I33" s="89" t="s">
+      <c r="I33" s="26" t="s">
         <v>117</v>
       </c>
       <c r="J33" s="51"/>
@@ -2519,23 +2508,23 @@
       <c r="P33" s="46"/>
     </row>
     <row r="34" spans="2:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="68" t="s">
+      <c r="B34" s="69" t="s">
         <v>1</v>
       </c>
       <c r="C34" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="87" t="s">
+      <c r="D34" s="48" t="s">
         <v>94</v>
       </c>
       <c r="E34" s="42"/>
-      <c r="G34" s="59" t="s">
+      <c r="G34" s="85" t="s">
         <v>33</v>
       </c>
       <c r="H34" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="90" t="s">
+      <c r="I34" s="36" t="s">
         <v>118</v>
       </c>
       <c r="J34" s="37" t="s">
@@ -2544,21 +2533,21 @@
       <c r="P34" s="46"/>
     </row>
     <row r="35" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B35" s="68"/>
+      <c r="B35" s="69"/>
       <c r="C35" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="81" t="s">
+      <c r="D35" s="24" t="s">
         <v>112</v>
       </c>
       <c r="E35" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="G35" s="60"/>
+      <c r="G35" s="73"/>
       <c r="H35" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="81" t="s">
+      <c r="I35" s="24" t="s">
         <v>126</v>
       </c>
       <c r="J35" s="15" t="s">
@@ -2568,44 +2557,44 @@
       <c r="P35" s="46"/>
     </row>
     <row r="36" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="69"/>
+      <c r="B36" s="71"/>
       <c r="C36" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="89" t="s">
+      <c r="D36" s="26" t="s">
         <v>93</v>
       </c>
       <c r="E36" s="51"/>
-      <c r="G36" s="61"/>
+      <c r="G36" s="74"/>
       <c r="H36" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="89"/>
+      <c r="I36" s="26"/>
       <c r="J36" s="51"/>
       <c r="L36" s="23"/>
       <c r="P36" s="46"/>
       <c r="Q36" s="47"/>
     </row>
     <row r="37" spans="2:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="70" t="s">
+      <c r="B37" s="86" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="87" t="s">
+      <c r="D37" s="48" t="s">
         <v>110</v>
       </c>
       <c r="E37" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="G37" s="59" t="s">
+      <c r="G37" s="85" t="s">
         <v>34</v>
       </c>
       <c r="H37" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I37" s="87" t="s">
+      <c r="I37" s="48" t="s">
         <v>150</v>
       </c>
       <c r="J37" s="37"/>
@@ -2613,19 +2602,19 @@
       <c r="Q37" s="47"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B38" s="68"/>
+      <c r="B38" s="69"/>
       <c r="C38" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="81" t="s">
+      <c r="D38" s="24" t="s">
         <v>91</v>
       </c>
       <c r="E38" s="15"/>
-      <c r="G38" s="60"/>
+      <c r="G38" s="73"/>
       <c r="H38" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I38" s="81" t="s">
+      <c r="I38" s="24" t="s">
         <v>127</v>
       </c>
       <c r="J38" s="15"/>
@@ -2634,65 +2623,65 @@
       <c r="Q38" s="47"/>
     </row>
     <row r="39" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="69"/>
+      <c r="B39" s="71"/>
       <c r="C39" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D39" s="89" t="s">
+      <c r="D39" s="26" t="s">
         <v>170</v>
       </c>
       <c r="E39" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="G39" s="61"/>
+      <c r="G39" s="74"/>
       <c r="H39" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I39" s="89"/>
+      <c r="I39" s="26"/>
       <c r="J39" s="50"/>
       <c r="L39" s="23"/>
       <c r="P39" s="46"/>
       <c r="Q39" s="47"/>
     </row>
     <row r="40" spans="2:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="70" t="s">
+      <c r="B40" s="86" t="s">
         <v>3</v>
       </c>
       <c r="C40" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D40" s="87" t="s">
+      <c r="D40" s="48" t="s">
         <v>156</v>
       </c>
       <c r="E40" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="G40" s="62" t="s">
+      <c r="G40" s="87" t="s">
         <v>35</v>
       </c>
       <c r="H40" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="I40" s="87" t="s">
+      <c r="I40" s="48" t="s">
         <v>149</v>
       </c>
       <c r="J40" s="42"/>
       <c r="P40" s="46"/>
     </row>
     <row r="41" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B41" s="68"/>
+      <c r="B41" s="69"/>
       <c r="C41" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="81" t="s">
+      <c r="D41" s="24" t="s">
         <v>111</v>
       </c>
       <c r="E41" s="15"/>
-      <c r="G41" s="60"/>
+      <c r="G41" s="73"/>
       <c r="H41" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I41" s="81" t="s">
+      <c r="I41" s="24" t="s">
         <v>128</v>
       </c>
       <c r="J41" s="15" t="s">
@@ -2702,47 +2691,46 @@
       <c r="P41" s="46"/>
     </row>
     <row r="42" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="71"/>
+      <c r="B42" s="70"/>
       <c r="C42" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D42" s="82" t="s">
+      <c r="D42" s="19" t="s">
         <v>155</v>
       </c>
       <c r="E42" s="52" t="s">
         <v>92</v>
       </c>
-      <c r="G42" s="63"/>
+      <c r="G42" s="88"/>
       <c r="H42" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I42" s="82"/>
+      <c r="I42" s="19"/>
       <c r="J42" s="20"/>
       <c r="L42" s="23"/>
       <c r="P42" s="46"/>
     </row>
     <row r="43" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D43" s="83"/>
       <c r="G43" s="23"/>
-      <c r="I43" s="96"/>
+      <c r="I43" s="46"/>
       <c r="P43" s="46"/>
     </row>
     <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B44" s="64" t="s">
+      <c r="B44" s="72" t="s">
         <v>14</v>
       </c>
       <c r="C44" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="85"/>
+      <c r="D44" s="21"/>
       <c r="E44" s="22"/>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="72" t="s">
         <v>36</v>
       </c>
       <c r="H44" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I44" s="85" t="s">
+      <c r="I44" s="21" t="s">
         <v>138</v>
       </c>
       <c r="J44" s="22" t="s">
@@ -2752,19 +2740,19 @@
       <c r="P44" s="46"/>
     </row>
     <row r="45" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B45" s="60"/>
+      <c r="B45" s="73"/>
       <c r="C45" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D45" s="81" t="s">
+      <c r="D45" s="24" t="s">
         <v>96</v>
       </c>
       <c r="E45" s="15"/>
-      <c r="G45" s="60"/>
+      <c r="G45" s="73"/>
       <c r="H45" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I45" s="81" t="s">
+      <c r="I45" s="24" t="s">
         <v>119</v>
       </c>
       <c r="J45" s="15" t="s">
@@ -2773,17 +2761,17 @@
       <c r="L45" s="23"/>
     </row>
     <row r="46" spans="2:17" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="61"/>
+      <c r="B46" s="74"/>
       <c r="C46" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="89"/>
+      <c r="D46" s="26"/>
       <c r="E46" s="51"/>
-      <c r="G46" s="61"/>
+      <c r="G46" s="74"/>
       <c r="H46" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I46" s="89" t="s">
+      <c r="I46" s="26" t="s">
         <v>139</v>
       </c>
       <c r="J46" s="51" t="s">
@@ -2791,21 +2779,25 @@
       </c>
     </row>
     <row r="47" spans="2:17" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="59" t="s">
+      <c r="B47" s="85" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D47" s="81"/>
-      <c r="E47" s="37"/>
-      <c r="G47" s="59" t="s">
+      <c r="D47" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G47" s="85" t="s">
         <v>37</v>
       </c>
       <c r="H47" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="90" t="s">
+      <c r="I47" s="36" t="s">
         <v>140</v>
       </c>
       <c r="J47" s="37" t="s">
@@ -2814,21 +2806,21 @@
       <c r="L47" s="23"/>
     </row>
     <row r="48" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B48" s="60"/>
+      <c r="B48" s="73"/>
       <c r="C48" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D48" s="81" t="s">
+      <c r="D48" s="24" t="s">
         <v>192</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="G48" s="60"/>
+        <v>199</v>
+      </c>
+      <c r="G48" s="73"/>
       <c r="H48" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="81" t="s">
+      <c r="I48" s="24" t="s">
         <v>120</v>
       </c>
       <c r="J48" s="15" t="s">
@@ -2837,55 +2829,63 @@
       <c r="L48" s="23"/>
     </row>
     <row r="49" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="61"/>
+      <c r="B49" s="74"/>
       <c r="C49" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="89"/>
-      <c r="E49" s="51"/>
-      <c r="G49" s="61"/>
+      <c r="D49" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="E49" s="51" t="s">
+        <v>201</v>
+      </c>
+      <c r="G49" s="74"/>
       <c r="H49" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I49" s="89"/>
+      <c r="I49" s="26"/>
       <c r="J49" s="51"/>
     </row>
     <row r="50" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="85" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="90"/>
-      <c r="E50" s="37"/>
-      <c r="G50" s="59" t="s">
+      <c r="D50" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="E50" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" s="85" t="s">
         <v>38</v>
       </c>
       <c r="H50" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I50" s="90" t="s">
+      <c r="I50" s="36" t="s">
         <v>131</v>
       </c>
       <c r="J50" s="37"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B51" s="60"/>
+      <c r="B51" s="73"/>
       <c r="C51" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D51" s="81" t="s">
+      <c r="D51" s="24" t="s">
         <v>97</v>
       </c>
       <c r="E51" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="G51" s="60"/>
+      <c r="G51" s="73"/>
       <c r="H51" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I51" s="81" t="s">
+      <c r="I51" s="24" t="s">
         <v>121</v>
       </c>
       <c r="J51" s="15" t="s">
@@ -2893,55 +2893,55 @@
       </c>
     </row>
     <row r="52" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="61"/>
+      <c r="B52" s="74"/>
       <c r="C52" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="89"/>
+      <c r="D52" s="26"/>
       <c r="E52" s="51"/>
-      <c r="G52" s="61"/>
+      <c r="G52" s="74"/>
       <c r="H52" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I52" s="89"/>
+      <c r="I52" s="26"/>
       <c r="J52" s="51"/>
     </row>
     <row r="53" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B53" s="59" t="s">
+      <c r="B53" s="85" t="s">
         <v>17</v>
       </c>
       <c r="C53" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D53" s="90"/>
+      <c r="D53" s="36"/>
       <c r="E53" s="37"/>
-      <c r="G53" s="62" t="s">
+      <c r="G53" s="87" t="s">
         <v>39</v>
       </c>
       <c r="H53" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="I53" s="87" t="s">
+      <c r="I53" s="48" t="s">
         <v>130</v>
       </c>
       <c r="J53" s="42"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B54" s="60"/>
+      <c r="B54" s="73"/>
       <c r="C54" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D54" s="81" t="s">
+      <c r="D54" s="24" t="s">
         <v>151</v>
       </c>
       <c r="E54" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G54" s="60"/>
+      <c r="G54" s="73"/>
       <c r="H54" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I54" s="81" t="s">
+      <c r="I54" s="24" t="s">
         <v>122</v>
       </c>
       <c r="J54" s="15" t="s">
@@ -2949,13 +2949,13 @@
       </c>
     </row>
     <row r="55" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="61"/>
+      <c r="B55" s="74"/>
       <c r="C55" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D55" s="89"/>
+      <c r="D55" s="26"/>
       <c r="E55" s="51"/>
-      <c r="G55" s="63"/>
+      <c r="G55" s="88"/>
       <c r="H55" s="19" t="s">
         <v>62</v>
       </c>
@@ -2963,27 +2963,27 @@
       <c r="J55" s="20"/>
     </row>
     <row r="56" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="59" t="s">
+      <c r="B56" s="85" t="s">
         <v>18</v>
       </c>
       <c r="C56" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D56" s="90"/>
+      <c r="D56" s="36"/>
       <c r="E56" s="37"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B57" s="60"/>
+      <c r="B57" s="73"/>
       <c r="C57" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D57" s="81" t="s">
+      <c r="D57" s="24" t="s">
         <v>176</v>
       </c>
       <c r="E57" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="G57" s="64" t="s">
+      <c r="G57" s="72" t="s">
         <v>40</v>
       </c>
       <c r="H57" s="21" t="s">
@@ -2997,13 +2997,13 @@
       </c>
     </row>
     <row r="58" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="61"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D58" s="89"/>
+      <c r="D58" s="26"/>
       <c r="E58" s="51"/>
-      <c r="G58" s="60"/>
+      <c r="G58" s="73"/>
       <c r="H58" s="24" t="s">
         <v>60</v>
       </c>
@@ -3015,15 +3015,15 @@
       </c>
     </row>
     <row r="59" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="62" t="s">
+      <c r="B59" s="87" t="s">
         <v>19</v>
       </c>
       <c r="C59" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D59" s="87"/>
+      <c r="D59" s="48"/>
       <c r="E59" s="42"/>
-      <c r="G59" s="61"/>
+      <c r="G59" s="74"/>
       <c r="H59" s="26" t="s">
         <v>62</v>
       </c>
@@ -3035,15 +3035,15 @@
       </c>
     </row>
     <row r="60" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="60"/>
+      <c r="B60" s="73"/>
       <c r="C60" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D60" s="88" t="s">
+      <c r="D60" s="61" t="s">
         <v>98</v>
       </c>
       <c r="E60" s="15"/>
-      <c r="G60" s="59" t="s">
+      <c r="G60" s="85" t="s">
         <v>41</v>
       </c>
       <c r="H60" s="36" t="s">
@@ -3053,21 +3053,21 @@
       <c r="J60" s="37"/>
     </row>
     <row r="61" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="63"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D61" s="82" t="s">
+      <c r="D61" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E61" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="E61" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="G61" s="60"/>
+      <c r="G61" s="73"/>
       <c r="H61" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I61" s="81" t="s">
+      <c r="I61" s="24" t="s">
         <v>141</v>
       </c>
       <c r="J61" s="15" t="s">
@@ -3075,46 +3075,51 @@
       </c>
     </row>
     <row r="62" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D62" s="83"/>
-      <c r="G62" s="61"/>
+      <c r="G62" s="74"/>
       <c r="H62" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I62" s="89"/>
+      <c r="I62" s="26"/>
       <c r="J62" s="51"/>
     </row>
     <row r="63" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="64" t="s">
+      <c r="B63" s="72" t="s">
         <v>20</v>
       </c>
       <c r="C63" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="D63" s="91"/>
-      <c r="E63" s="22"/>
-      <c r="G63" s="59" t="s">
+      <c r="D63" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="G63" s="85" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="I63" s="90"/>
+      <c r="I63" s="36"/>
       <c r="J63" s="37"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B64" s="60"/>
+      <c r="B64" s="73"/>
       <c r="C64" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D64" s="81" t="s">
-        <v>177</v>
-      </c>
-      <c r="E64" s="15"/>
-      <c r="G64" s="60"/>
+      <c r="D64" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="G64" s="73"/>
       <c r="H64" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I64" s="81" t="s">
+      <c r="I64" s="24" t="s">
         <v>142</v>
       </c>
       <c r="J64" s="15" t="s">
@@ -3122,49 +3127,53 @@
       </c>
     </row>
     <row r="65" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="61"/>
+      <c r="B65" s="74"/>
       <c r="C65" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D65" s="89"/>
+      <c r="D65" s="26"/>
       <c r="E65" s="51"/>
-      <c r="G65" s="61"/>
+      <c r="G65" s="74"/>
       <c r="H65" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="I65" s="89"/>
+      <c r="I65" s="26"/>
       <c r="J65" s="51"/>
     </row>
     <row r="66" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="59" t="s">
+      <c r="B66" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C66" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D66" s="90"/>
+      <c r="D66" s="36"/>
       <c r="E66" s="37"/>
-      <c r="G66" s="62" t="s">
+      <c r="G66" s="87" t="s">
         <v>43</v>
       </c>
       <c r="H66" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="I66" s="87"/>
+      <c r="I66" s="48"/>
       <c r="J66" s="42"/>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B67" s="60"/>
+      <c r="B67" s="73"/>
       <c r="C67" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D67" s="81"/>
-      <c r="E67" s="15"/>
-      <c r="G67" s="60"/>
+      <c r="D67" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" s="73"/>
       <c r="H67" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="I67" s="81" t="s">
+      <c r="I67" s="24" t="s">
         <v>124</v>
       </c>
       <c r="J67" s="15" t="s">
@@ -3172,63 +3181,63 @@
       </c>
     </row>
     <row r="68" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="61"/>
+      <c r="B68" s="74"/>
       <c r="C68" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D68" s="89"/>
+      <c r="D68" s="26"/>
       <c r="E68" s="51"/>
-      <c r="G68" s="63"/>
+      <c r="G68" s="88"/>
       <c r="H68" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I68" s="82"/>
+      <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
     <row r="69" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="59" t="s">
+      <c r="B69" s="85" t="s">
         <v>22</v>
       </c>
       <c r="C69" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D69" s="90"/>
+      <c r="D69" s="36"/>
       <c r="E69" s="37"/>
     </row>
     <row r="70" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="60"/>
+      <c r="B70" s="73"/>
       <c r="C70" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D70" s="81" t="s">
+      <c r="D70" s="24" t="s">
         <v>178</v>
       </c>
       <c r="E70" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="G70" s="65" t="s">
+      <c r="G70" s="79" t="s">
         <v>74</v>
       </c>
-      <c r="H70" s="66"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="67"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="80"/>
+      <c r="J70" s="81"/>
     </row>
     <row r="71" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="61"/>
+      <c r="B71" s="74"/>
       <c r="C71" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D71" s="89"/>
+      <c r="D71" s="26"/>
       <c r="E71" s="51"/>
     </row>
     <row r="72" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="59" t="s">
+      <c r="B72" s="85" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D72" s="85" t="s">
+      <c r="D72" s="21" t="s">
         <v>100</v>
       </c>
       <c r="E72" s="37"/>
@@ -3246,11 +3255,11 @@
       </c>
     </row>
     <row r="73" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B73" s="60"/>
+      <c r="B73" s="73"/>
       <c r="C73" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D73" s="81" t="s">
+      <c r="D73" s="24" t="s">
         <v>99</v>
       </c>
       <c r="E73" s="15"/>
@@ -3260,7 +3269,7 @@
       <c r="H73" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I73" s="81" t="s">
+      <c r="I73" s="24" t="s">
         <v>56</v>
       </c>
       <c r="J73" s="12" t="s">
@@ -3268,11 +3277,11 @@
       </c>
     </row>
     <row r="74" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="61"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D74" s="87" t="s">
+      <c r="D74" s="48" t="s">
         <v>101</v>
       </c>
       <c r="E74" s="51"/>
@@ -3288,13 +3297,13 @@
       <c r="J74" s="15"/>
     </row>
     <row r="75" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="59" t="s">
+      <c r="B75" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D75" s="90"/>
+      <c r="D75" s="36"/>
       <c r="E75" s="37"/>
       <c r="G75" s="53" t="s">
         <v>78</v>
@@ -3308,11 +3317,11 @@
       <c r="J75" s="20"/>
     </row>
     <row r="76" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="60"/>
+      <c r="B76" s="73"/>
       <c r="C76" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D76" s="81" t="s">
+      <c r="D76" s="24" t="s">
         <v>180</v>
       </c>
       <c r="E76" s="15" t="s">
@@ -3324,11 +3333,11 @@
       <c r="J76" s="54"/>
     </row>
     <row r="77" spans="2:10" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="61"/>
+      <c r="B77" s="74"/>
       <c r="C77" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="D77" s="89"/>
+      <c r="D77" s="26"/>
       <c r="E77" s="51"/>
       <c r="G77" s="55" t="s">
         <v>79</v>
@@ -3344,13 +3353,13 @@
       </c>
     </row>
     <row r="78" spans="2:10" ht="13.5" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="62" t="s">
+      <c r="B78" s="87" t="s">
         <v>25</v>
       </c>
       <c r="C78" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D78" s="87" t="s">
+      <c r="D78" s="48" t="s">
         <v>134</v>
       </c>
       <c r="E78" s="42" t="s">
@@ -3368,11 +3377,11 @@
       <c r="J78" s="15"/>
     </row>
     <row r="79" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="60"/>
+      <c r="B79" s="73"/>
       <c r="C79" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="D79" s="81" t="s">
+      <c r="D79" s="24" t="s">
         <v>135</v>
       </c>
       <c r="E79" s="15" t="s">
@@ -3390,11 +3399,11 @@
       <c r="J79" s="20"/>
     </row>
     <row r="80" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="63"/>
+      <c r="B80" s="88"/>
       <c r="C80" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D80" s="82" t="s">
+      <c r="D80" s="19" t="s">
         <v>133</v>
       </c>
       <c r="E80" s="20" t="s">
@@ -3403,31 +3412,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="G15:G17"/>
-    <mergeCell ref="G20:G22"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="G27:G29"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="B50:B52"/>
-    <mergeCell ref="B53:B55"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B44:B46"/>
-    <mergeCell ref="B47:B49"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G37:G39"/>
-    <mergeCell ref="G40:G42"/>
-    <mergeCell ref="G44:G46"/>
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B78:B80"/>
@@ -3443,6 +3427,31 @@
     <mergeCell ref="B66:B68"/>
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="G70:J70"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B53:B55"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G37:G39"/>
+    <mergeCell ref="G40:G42"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="G15:G17"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="G27:G29"/>
+    <mergeCell ref="G31:G33"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
